--- a/data/dividends_info_20260428.xlsx
+++ b/data/dividends_info_20260428.xlsx
@@ -523,10 +523,10 @@
         </is>
       </c>
       <c r="H2" t="n">
-        <v>43.45999908447266</v>
+        <v>42.19499969482422</v>
       </c>
       <c r="I2" t="n">
-        <v>0.2070869808926322</v>
+        <v>0.2132954156912571</v>
       </c>
       <c r="J2" t="n">
         <v>321</v>
@@ -570,10 +570,10 @@
         </is>
       </c>
       <c r="H3" t="n">
-        <v>56.59999847412109</v>
+        <v>56.45000076293945</v>
       </c>
       <c r="I3" t="n">
-        <v>1.236749149949283</v>
+        <v>1.240035412824235</v>
       </c>
       <c r="J3" t="n">
         <v>300</v>
@@ -617,10 +617,10 @@
         </is>
       </c>
       <c r="H4" t="n">
-        <v>9.220000267028809</v>
+        <v>9.380000114440918</v>
       </c>
       <c r="I4" t="n">
-        <v>0.6507592002417079</v>
+        <v>0.6396588408098992</v>
       </c>
       <c r="J4" t="n">
         <v>230</v>
@@ -711,10 +711,10 @@
         </is>
       </c>
       <c r="H6" t="n">
-        <v>43.45999908447266</v>
+        <v>42.19499969482422</v>
       </c>
       <c r="I6" t="n">
-        <v>0.2070869808926322</v>
+        <v>0.2132954156912571</v>
       </c>
       <c r="J6" t="n">
         <v>230</v>
@@ -805,10 +805,10 @@
         </is>
       </c>
       <c r="H8" t="n">
-        <v>6</v>
+        <v>5.989999771118164</v>
       </c>
       <c r="I8" t="n">
-        <v>3.333333333333333</v>
+        <v>3.338898291187508</v>
       </c>
       <c r="J8" t="n">
         <v>202</v>
@@ -852,10 +852,10 @@
         </is>
       </c>
       <c r="H9" t="n">
-        <v>5.800000190734863</v>
+        <v>5.900000095367432</v>
       </c>
       <c r="I9" t="n">
-        <v>1.034482724601393</v>
+        <v>1.016949136104436</v>
       </c>
       <c r="J9" t="n">
         <v>174</v>
@@ -946,10 +946,10 @@
         </is>
       </c>
       <c r="H11" t="n">
-        <v>4.940000057220459</v>
+        <v>4.929999828338623</v>
       </c>
       <c r="I11" t="n">
-        <v>0.7692307603207009</v>
+        <v>0.7707911018894649</v>
       </c>
       <c r="J11" t="n">
         <v>153</v>
@@ -993,10 +993,10 @@
         </is>
       </c>
       <c r="H12" t="n">
-        <v>43.45999908447266</v>
+        <v>42.19499969482422</v>
       </c>
       <c r="I12" t="n">
-        <v>0.2070869808926322</v>
+        <v>0.2132954156912571</v>
       </c>
       <c r="J12" t="n">
         <v>146</v>
@@ -1087,10 +1087,10 @@
         </is>
       </c>
       <c r="H14" t="n">
-        <v>4.940000057220459</v>
+        <v>4.929999828338623</v>
       </c>
       <c r="I14" t="n">
-        <v>0.7692307603207009</v>
+        <v>0.7707911018894649</v>
       </c>
       <c r="J14" t="n">
         <v>97</v>
@@ -1181,10 +1181,10 @@
         </is>
       </c>
       <c r="H16" t="n">
-        <v>9.864999771118164</v>
+        <v>9.944999694824219</v>
       </c>
       <c r="I16" t="n">
-        <v>2.635580395665127</v>
+        <v>2.614379165193082</v>
       </c>
       <c r="J16" t="n">
         <v>83</v>
@@ -1228,10 +1228,10 @@
         </is>
       </c>
       <c r="H17" t="n">
-        <v>16.26000022888184</v>
+        <v>16.20000076293945</v>
       </c>
       <c r="I17" t="n">
-        <v>3.690036848426666</v>
+        <v>3.703703529277682</v>
       </c>
       <c r="J17" t="n">
         <v>83</v>
@@ -1275,10 +1275,10 @@
         </is>
       </c>
       <c r="H18" t="n">
-        <v>3.788000106811523</v>
+        <v>3.782000064849854</v>
       </c>
       <c r="I18" t="n">
-        <v>5.807813986182297</v>
+        <v>5.817027927754255</v>
       </c>
       <c r="J18" t="n">
         <v>83</v>
@@ -1369,10 +1369,10 @@
         </is>
       </c>
       <c r="H20" t="n">
-        <v>6.014999866485596</v>
+        <v>5.909999847412109</v>
       </c>
       <c r="I20" t="n">
-        <v>1.662510427592534</v>
+        <v>1.692047421012851</v>
       </c>
       <c r="J20" t="n">
         <v>83</v>
@@ -1463,10 +1463,10 @@
         </is>
       </c>
       <c r="H22" t="n">
-        <v>5.489999771118164</v>
+        <v>5.510000228881836</v>
       </c>
       <c r="I22" t="n">
-        <v>2.18579244085395</v>
+        <v>2.177858348734625</v>
       </c>
       <c r="J22" t="n">
         <v>76</v>
@@ -1510,10 +1510,10 @@
         </is>
       </c>
       <c r="H23" t="n">
-        <v>9.350000381469727</v>
+        <v>9.5</v>
       </c>
       <c r="I23" t="n">
-        <v>0.5347593364711767</v>
+        <v>0.5263157894736842</v>
       </c>
       <c r="J23" t="n">
         <v>76</v>
@@ -1604,10 +1604,10 @@
         </is>
       </c>
       <c r="H25" t="n">
-        <v>4.269999980926514</v>
+        <v>4.369999885559082</v>
       </c>
       <c r="I25" t="n">
-        <v>1.639344269617801</v>
+        <v>1.601830705564068</v>
       </c>
       <c r="J25" t="n">
         <v>69</v>
@@ -1651,10 +1651,10 @@
         </is>
       </c>
       <c r="H26" t="n">
-        <v>34.29999923706055</v>
+        <v>34.40000152587891</v>
       </c>
       <c r="I26" t="n">
-        <v>0.4373177939838775</v>
+        <v>0.4360464922862167</v>
       </c>
       <c r="J26" t="n">
         <v>69</v>
@@ -1745,10 +1745,10 @@
         </is>
       </c>
       <c r="H28" t="n">
-        <v>23.07999992370605</v>
+        <v>22.8799991607666</v>
       </c>
       <c r="I28" t="n">
-        <v>4.11611786455957</v>
+        <v>4.15209805439595</v>
       </c>
       <c r="J28" t="n">
         <v>55</v>
@@ -1792,10 +1792,10 @@
         </is>
       </c>
       <c r="H29" t="n">
-        <v>25.95000076293945</v>
+        <v>25.70000076293945</v>
       </c>
       <c r="I29" t="n">
-        <v>0.7514450646124436</v>
+        <v>0.7587548412885602</v>
       </c>
       <c r="J29" t="n">
         <v>55</v>
@@ -1933,10 +1933,10 @@
         </is>
       </c>
       <c r="H32" t="n">
-        <v>4.105999946594238</v>
+        <v>4.096000194549561</v>
       </c>
       <c r="I32" t="n">
-        <v>3.896736533879245</v>
+        <v>3.90624981446309</v>
       </c>
       <c r="J32" t="n">
         <v>55</v>
@@ -1980,10 +1980,10 @@
         </is>
       </c>
       <c r="H33" t="n">
-        <v>2.664000034332275</v>
+        <v>2.628000020980835</v>
       </c>
       <c r="I33" t="n">
-        <v>5.202702635652921</v>
+        <v>5.273972560634571</v>
       </c>
       <c r="J33" t="n">
         <v>55</v>
@@ -2027,10 +2027,10 @@
         </is>
       </c>
       <c r="H34" t="n">
-        <v>52.13999938964844</v>
+        <v>52.40999984741211</v>
       </c>
       <c r="I34" t="n">
-        <v>1.208285399644781</v>
+        <v>1.20206067894333</v>
       </c>
       <c r="J34" t="n">
         <v>55</v>
@@ -2074,10 +2074,10 @@
         </is>
       </c>
       <c r="H35" t="n">
-        <v>5.139999866485596</v>
+        <v>5.090000152587891</v>
       </c>
       <c r="I35" t="n">
-        <v>2.723735479310879</v>
+        <v>2.750491076681409</v>
       </c>
       <c r="J35" t="n">
         <v>55</v>
@@ -2168,10 +2168,10 @@
         </is>
       </c>
       <c r="H37" t="n">
-        <v>22.44000053405762</v>
+        <v>22.5</v>
       </c>
       <c r="I37" t="n">
-        <v>3.787878697729703</v>
+        <v>3.777777777777778</v>
       </c>
       <c r="J37" t="n">
         <v>55</v>
@@ -2215,10 +2215,10 @@
         </is>
       </c>
       <c r="H38" t="n">
-        <v>43.45999908447266</v>
+        <v>42.19499969482422</v>
       </c>
       <c r="I38" t="n">
-        <v>0.2070869808926322</v>
+        <v>0.2132954156912571</v>
       </c>
       <c r="J38" t="n">
         <v>55</v>
@@ -2262,10 +2262,10 @@
         </is>
       </c>
       <c r="H39" t="n">
-        <v>6.676000118255615</v>
+        <v>6.699999809265137</v>
       </c>
       <c r="I39" t="n">
-        <v>2.715697974663491</v>
+        <v>2.705970226286994</v>
       </c>
       <c r="J39" t="n">
         <v>55</v>
@@ -2309,10 +2309,10 @@
         </is>
       </c>
       <c r="H40" t="n">
-        <v>8.520000457763672</v>
+        <v>8.479999542236328</v>
       </c>
       <c r="I40" t="n">
-        <v>3.051643028529188</v>
+        <v>3.066037901358581</v>
       </c>
       <c r="J40" t="n">
         <v>55</v>
@@ -2356,10 +2356,10 @@
         </is>
       </c>
       <c r="H41" t="n">
-        <v>10.23999977111816</v>
+        <v>10.27000045776367</v>
       </c>
       <c r="I41" t="n">
-        <v>2.70507818546321</v>
+        <v>2.697176121259081</v>
       </c>
       <c r="J41" t="n">
         <v>55</v>
@@ -2403,10 +2403,10 @@
         </is>
       </c>
       <c r="H42" t="n">
-        <v>1.179999947547913</v>
+        <v>1.159999966621399</v>
       </c>
       <c r="I42" t="n">
-        <v>1.14406784746504</v>
+        <v>1.163793136936023</v>
       </c>
       <c r="J42" t="n">
         <v>48</v>
@@ -2450,10 +2450,10 @@
         </is>
       </c>
       <c r="H43" t="n">
-        <v>4.070000171661377</v>
+        <v>4.156000137329102</v>
       </c>
       <c r="I43" t="n">
-        <v>2.702702588710161</v>
+        <v>2.646775658450596</v>
       </c>
       <c r="J43" t="n">
         <v>48</v>
@@ -2497,10 +2497,10 @@
         </is>
       </c>
       <c r="H44" t="n">
-        <v>2.480000019073486</v>
+        <v>2.420000076293945</v>
       </c>
       <c r="I44" t="n">
-        <v>0.9677419280410434</v>
+        <v>0.991735505924209</v>
       </c>
       <c r="J44" t="n">
         <v>48</v>
@@ -2544,10 +2544,10 @@
         </is>
       </c>
       <c r="H45" t="n">
-        <v>3.440000057220459</v>
+        <v>3.454999923706055</v>
       </c>
       <c r="I45" t="n">
-        <v>4.651162713330911</v>
+        <v>4.630969711523864</v>
       </c>
       <c r="J45" t="n">
         <v>41</v>
@@ -2591,10 +2591,10 @@
         </is>
       </c>
       <c r="H46" t="n">
-        <v>0.9300000071525574</v>
+        <v>0.925000011920929</v>
       </c>
       <c r="I46" t="n">
-        <v>2.688172022336232</v>
+        <v>2.702702667871647</v>
       </c>
       <c r="J46" t="n">
         <v>41</v>
@@ -2638,10 +2638,10 @@
         </is>
       </c>
       <c r="H47" t="n">
-        <v>28.35000038146973</v>
+        <v>28.25</v>
       </c>
       <c r="I47" t="n">
-        <v>3.915343862660136</v>
+        <v>3.929203539823009</v>
       </c>
       <c r="J47" t="n">
         <v>37</v>
@@ -2685,10 +2685,10 @@
         </is>
       </c>
       <c r="H48" t="n">
-        <v>0.9100000262260437</v>
+        <v>0.9039999842643738</v>
       </c>
       <c r="I48" t="n">
-        <v>3.296703201692877</v>
+        <v>3.318584128561946</v>
       </c>
       <c r="J48" t="n">
         <v>34</v>
@@ -2732,10 +2732,10 @@
         </is>
       </c>
       <c r="H49" t="n">
-        <v>0.5130000114440918</v>
+        <v>0.5099999904632568</v>
       </c>
       <c r="I49" t="n">
-        <v>4.483430699203134</v>
+        <v>4.509804005899691</v>
       </c>
       <c r="J49" t="n">
         <v>34</v>
@@ -2779,10 +2779,10 @@
         </is>
       </c>
       <c r="H50" t="n">
-        <v>18.79999923706055</v>
+        <v>19</v>
       </c>
       <c r="I50" t="n">
-        <v>3.191489491218789</v>
+        <v>3.157894736842105</v>
       </c>
       <c r="J50" t="n">
         <v>34</v>
@@ -2873,10 +2873,10 @@
         </is>
       </c>
       <c r="H52" t="n">
-        <v>2.569999933242798</v>
+        <v>2.549999952316284</v>
       </c>
       <c r="I52" t="n">
-        <v>7.00389123251369</v>
+        <v>7.058823661408212</v>
       </c>
       <c r="J52" t="n">
         <v>27</v>
@@ -2967,10 +2967,10 @@
         </is>
       </c>
       <c r="H54" t="n">
-        <v>13.07999992370605</v>
+        <v>13.05000019073486</v>
       </c>
       <c r="I54" t="n">
-        <v>1.911314995857933</v>
+        <v>1.915708784261115</v>
       </c>
       <c r="J54" t="n">
         <v>27</v>
@@ -3014,10 +3014,10 @@
         </is>
       </c>
       <c r="H55" t="n">
-        <v>3.299999952316284</v>
+        <v>3.339999914169312</v>
       </c>
       <c r="I55" t="n">
-        <v>0.909090922226919</v>
+        <v>0.8982036158962379</v>
       </c>
       <c r="J55" t="n">
         <v>27</v>
@@ -3061,10 +3061,10 @@
         </is>
       </c>
       <c r="H56" t="n">
-        <v>3.799999952316284</v>
+        <v>3.769999980926514</v>
       </c>
       <c r="I56" t="n">
-        <v>3.947368470585578</v>
+        <v>3.978779860978569</v>
       </c>
       <c r="J56" t="n">
         <v>27</v>
@@ -3108,10 +3108,10 @@
         </is>
       </c>
       <c r="H57" t="n">
-        <v>13.69999980926514</v>
+        <v>13.80000019073486</v>
       </c>
       <c r="I57" t="n">
-        <v>4.233576701276691</v>
+        <v>4.202898492634835</v>
       </c>
       <c r="J57" t="n">
         <v>27</v>
@@ -3155,10 +3155,10 @@
         </is>
       </c>
       <c r="H58" t="n">
-        <v>2.407000064849854</v>
+        <v>2.385999917984009</v>
       </c>
       <c r="I58" t="n">
-        <v>4.320731084254766</v>
+        <v>4.358759579835702</v>
       </c>
       <c r="J58" t="n">
         <v>20</v>
@@ -3296,10 +3296,10 @@
         </is>
       </c>
       <c r="H61" t="n">
-        <v>38.20000076293945</v>
+        <v>38.36999893188477</v>
       </c>
       <c r="I61" t="n">
-        <v>4.293193631532806</v>
+        <v>4.27417264960409</v>
       </c>
       <c r="J61" t="n">
         <v>20</v>
@@ -3343,10 +3343,10 @@
         </is>
       </c>
       <c r="H62" t="n">
-        <v>36.9900016784668</v>
+        <v>36.4900016784668</v>
       </c>
       <c r="I62" t="n">
-        <v>5.406866475392111</v>
+        <v>5.480953433828492</v>
       </c>
       <c r="J62" t="n">
         <v>20</v>
@@ -3390,10 +3390,10 @@
         </is>
       </c>
       <c r="H63" t="n">
-        <v>3.946000099182129</v>
+        <v>3.907999992370605</v>
       </c>
       <c r="I63" t="n">
-        <v>2.534211796414465</v>
+        <v>2.558853638567683</v>
       </c>
       <c r="J63" t="n">
         <v>20</v>
@@ -3437,10 +3437,10 @@
         </is>
       </c>
       <c r="H64" t="n">
-        <v>30.6200008392334</v>
+        <v>30.71999931335449</v>
       </c>
       <c r="I64" t="n">
-        <v>0.4848464922632472</v>
+        <v>0.4832682399685536</v>
       </c>
       <c r="J64" t="n">
         <v>20</v>
@@ -3484,10 +3484,10 @@
         </is>
       </c>
       <c r="H65" t="n">
-        <v>23.36000061035156</v>
+        <v>23.21999931335449</v>
       </c>
       <c r="I65" t="n">
-        <v>3.938356061481945</v>
+        <v>3.962101753684728</v>
       </c>
       <c r="J65" t="n">
         <v>20</v>
@@ -3531,10 +3531,10 @@
         </is>
       </c>
       <c r="H66" t="n">
-        <v>8.229999542236328</v>
+        <v>8.130000114440918</v>
       </c>
       <c r="I66" t="n">
-        <v>3.645200688777698</v>
+        <v>3.690036848426666</v>
       </c>
       <c r="J66" t="n">
         <v>20</v>
@@ -3578,10 +3578,10 @@
         </is>
       </c>
       <c r="H67" t="n">
-        <v>83.48000335693359</v>
+        <v>82.87999725341797</v>
       </c>
       <c r="I67" t="n">
-        <v>1.245807328915998</v>
+        <v>1.254826296410272</v>
       </c>
       <c r="J67" t="n">
         <v>20</v>
@@ -3625,10 +3625,10 @@
         </is>
       </c>
       <c r="H68" t="n">
-        <v>47.47999954223633</v>
+        <v>46.54999923706055</v>
       </c>
       <c r="I68" t="n">
-        <v>1.474304984727954</v>
+        <v>1.503759423142371</v>
       </c>
       <c r="J68" t="n">
         <v>20</v>
@@ -3672,10 +3672,10 @@
         </is>
       </c>
       <c r="H69" t="n">
-        <v>56.59999847412109</v>
+        <v>56.45000076293945</v>
       </c>
       <c r="I69" t="n">
-        <v>3.886925899840606</v>
+        <v>3.897254154590453</v>
       </c>
       <c r="J69" t="n">
         <v>20</v>
@@ -3719,10 +3719,10 @@
         </is>
       </c>
       <c r="H70" t="n">
-        <v>9.133999824523926</v>
+        <v>9.100000381469727</v>
       </c>
       <c r="I70" t="n">
-        <v>9.415371321674227</v>
+        <v>9.450549054384796</v>
       </c>
       <c r="J70" t="n">
         <v>20</v>
@@ -3766,10 +3766,10 @@
         </is>
       </c>
       <c r="H71" t="n">
-        <v>12.45800018310547</v>
+        <v>12.46000003814697</v>
       </c>
       <c r="I71" t="n">
-        <v>4.495103481852784</v>
+        <v>4.494382008712114</v>
       </c>
       <c r="J71" t="n">
         <v>20</v>
@@ -3813,10 +3813,10 @@
         </is>
       </c>
       <c r="H72" t="n">
-        <v>2.180000066757202</v>
+        <v>2.240000009536743</v>
       </c>
       <c r="I72" t="n">
-        <v>1.834862329132901</v>
+        <v>1.785714278111652</v>
       </c>
       <c r="J72" t="n">
         <v>20</v>
@@ -3860,10 +3860,10 @@
         </is>
       </c>
       <c r="H73" t="n">
-        <v>9.479999542236328</v>
+        <v>9.329999923706055</v>
       </c>
       <c r="I73" t="n">
-        <v>3.164557114833258</v>
+        <v>3.215434109894765</v>
       </c>
       <c r="J73" t="n">
         <v>20</v>
@@ -3907,10 +3907,10 @@
         </is>
       </c>
       <c r="H74" t="n">
-        <v>2.220000028610229</v>
+        <v>2.230000019073486</v>
       </c>
       <c r="I74" t="n">
-        <v>4.864864802168965</v>
+        <v>4.843049285931015</v>
       </c>
       <c r="J74" t="n">
         <v>20</v>
@@ -3954,10 +3954,10 @@
         </is>
       </c>
       <c r="H75" t="n">
-        <v>73.30000305175781</v>
+        <v>72.59999847412109</v>
       </c>
       <c r="I75" t="n">
-        <v>2.81036823224334</v>
+        <v>2.837465624375055</v>
       </c>
       <c r="J75" t="n">
         <v>20</v>
@@ -4001,10 +4001,10 @@
         </is>
       </c>
       <c r="H76" t="n">
-        <v>15.23999977111816</v>
+        <v>15.14000034332275</v>
       </c>
       <c r="I76" t="n">
-        <v>4.921259916429594</v>
+        <v>4.95376474896036</v>
       </c>
       <c r="J76" t="n">
         <v>20</v>
@@ -4048,10 +4048,10 @@
         </is>
       </c>
       <c r="H77" t="n">
-        <v>15.60000038146973</v>
+        <v>15.39999961853027</v>
       </c>
       <c r="I77" t="n">
-        <v>1.923076876051564</v>
+        <v>1.948051996306679</v>
       </c>
       <c r="J77" t="n">
         <v>20</v>
@@ -4142,10 +4142,10 @@
         </is>
       </c>
       <c r="H79" t="n">
-        <v>34.15999984741211</v>
+        <v>33.79999923706055</v>
       </c>
       <c r="I79" t="n">
-        <v>2.488290409241305</v>
+        <v>2.514792956172626</v>
       </c>
       <c r="J79" t="n">
         <v>20</v>
@@ -4189,10 +4189,10 @@
         </is>
       </c>
       <c r="H80" t="n">
-        <v>58.06000137329102</v>
+        <v>57.93999862670898</v>
       </c>
       <c r="I80" t="n">
-        <v>2.239062985275834</v>
+        <v>2.243700432883218</v>
       </c>
       <c r="J80" t="n">
         <v>20</v>
@@ -4236,10 +4236,10 @@
         </is>
       </c>
       <c r="H81" t="n">
-        <v>8.079999923706055</v>
+        <v>8.100000381469727</v>
       </c>
       <c r="I81" t="n">
-        <v>7.425742644373663</v>
+        <v>7.407407058555364</v>
       </c>
       <c r="J81" t="n">
         <v>20</v>
@@ -4283,10 +4283,10 @@
         </is>
       </c>
       <c r="H82" t="n">
-        <v>6</v>
+        <v>6.150000095367432</v>
       </c>
       <c r="I82" t="n">
-        <v>7.833333333333332</v>
+        <v>7.642276304256217</v>
       </c>
       <c r="J82" t="n">
         <v>20</v>
@@ -4330,10 +4330,10 @@
         </is>
       </c>
       <c r="H83" t="n">
-        <v>6</v>
+        <v>5.989999771118164</v>
       </c>
       <c r="I83" t="n">
-        <v>3.333333333333333</v>
+        <v>3.338898291187508</v>
       </c>
       <c r="J83" t="n">
         <v>20</v>
@@ -4377,10 +4377,10 @@
         </is>
       </c>
       <c r="H84" t="n">
-        <v>22.63999938964844</v>
+        <v>22.73999977111816</v>
       </c>
       <c r="I84" t="n">
-        <v>4.416961249818869</v>
+        <v>4.397537423329659</v>
       </c>
       <c r="J84" t="n">
         <v>20</v>
@@ -4424,10 +4424,10 @@
         </is>
       </c>
       <c r="H85" t="n">
-        <v>4.800000190734863</v>
+        <v>4.929999828338623</v>
       </c>
       <c r="I85" t="n">
-        <v>4.479166488680582</v>
+        <v>4.361054918585131</v>
       </c>
       <c r="J85" t="n">
         <v>20</v>
@@ -4471,10 +4471,10 @@
         </is>
       </c>
       <c r="H86" t="n">
-        <v>23.6825008392334</v>
+        <v>23.41500091552734</v>
       </c>
       <c r="I86" t="n">
-        <v>1.140082298879124</v>
+        <v>1.153106937616873</v>
       </c>
       <c r="J86" t="n">
         <v>20</v>
@@ -4518,10 +4518,10 @@
         </is>
       </c>
       <c r="H87" t="n">
-        <v>8.380000114440918</v>
+        <v>8.479999542236328</v>
       </c>
       <c r="I87" t="n">
-        <v>2.386634812275814</v>
+        <v>2.358490693352755</v>
       </c>
       <c r="J87" t="n">
         <v>20</v>
@@ -4565,10 +4565,10 @@
         </is>
       </c>
       <c r="H88" t="n">
-        <v>9.479999542236328</v>
+        <v>9.350000381469727</v>
       </c>
       <c r="I88" t="n">
-        <v>2.531645691866606</v>
+        <v>2.566844815061648</v>
       </c>
       <c r="J88" t="n">
         <v>20</v>
@@ -4612,10 +4612,10 @@
         </is>
       </c>
       <c r="H89" t="n">
-        <v>21.28000068664551</v>
+        <v>21.25</v>
       </c>
       <c r="I89" t="n">
-        <v>3.71240589524874</v>
+        <v>3.71764705882353</v>
       </c>
       <c r="J89" t="n">
         <v>20</v>
@@ -4659,10 +4659,10 @@
         </is>
       </c>
       <c r="H90" t="n">
-        <v>5.099999904632568</v>
+        <v>5.059999942779541</v>
       </c>
       <c r="I90" t="n">
-        <v>1.823529445863788</v>
+        <v>1.837944684815818</v>
       </c>
       <c r="J90" t="n">
         <v>20</v>
@@ -4706,10 +4706,10 @@
         </is>
       </c>
       <c r="H91" t="n">
-        <v>5.800000190734863</v>
+        <v>5.900000095367432</v>
       </c>
       <c r="I91" t="n">
-        <v>1.034482724601393</v>
+        <v>1.016949136104436</v>
       </c>
       <c r="J91" t="n">
         <v>20</v>
@@ -4753,10 +4753,10 @@
         </is>
       </c>
       <c r="H92" t="n">
-        <v>36.58000183105469</v>
+        <v>35.93999862670898</v>
       </c>
       <c r="I92" t="n">
-        <v>0.9568069504656683</v>
+        <v>0.9738453349296896</v>
       </c>
       <c r="J92" t="n">
         <v>20</v>
@@ -4800,10 +4800,10 @@
         </is>
       </c>
       <c r="H93" t="n">
-        <v>7.434999942779541</v>
+        <v>7.324999809265137</v>
       </c>
       <c r="I93" t="n">
-        <v>7.455279142783389</v>
+        <v>7.567235691922958</v>
       </c>
       <c r="J93" t="n">
         <v>20</v>
@@ -4847,10 +4847,10 @@
         </is>
       </c>
       <c r="H94" t="n">
-        <v>2.200000047683716</v>
+        <v>2.259999990463257</v>
       </c>
       <c r="I94" t="n">
-        <v>2.727272668160684</v>
+        <v>2.654867267840171</v>
       </c>
       <c r="J94" t="n">
         <v>20</v>
@@ -4894,10 +4894,10 @@
         </is>
       </c>
       <c r="H95" t="n">
-        <v>12.5</v>
+        <v>12.35000038146973</v>
       </c>
       <c r="I95" t="n">
-        <v>1.6</v>
+        <v>1.619433148359132</v>
       </c>
       <c r="J95" t="n">
         <v>20</v>
@@ -4941,10 +4941,10 @@
         </is>
       </c>
       <c r="H96" t="n">
-        <v>6.150000095367432</v>
+        <v>6.09499979019165</v>
       </c>
       <c r="I96" t="n">
-        <v>1.674796721996575</v>
+        <v>1.689909820271893</v>
       </c>
       <c r="J96" t="n">
         <v>20</v>
@@ -4988,10 +4988,10 @@
         </is>
       </c>
       <c r="H97" t="n">
-        <v>5.730999946594238</v>
+        <v>5.781000137329102</v>
       </c>
       <c r="I97" t="n">
-        <v>3.315302770381481</v>
+        <v>3.286628532892277</v>
       </c>
       <c r="J97" t="n">
         <v>20</v>
@@ -5035,10 +5035,10 @@
         </is>
       </c>
       <c r="H98" t="n">
-        <v>10.34500026702881</v>
+        <v>10.35499954223633</v>
       </c>
       <c r="I98" t="n">
-        <v>4.175930293369387</v>
+        <v>4.171897818420402</v>
       </c>
       <c r="J98" t="n">
         <v>20</v>
@@ -5082,10 +5082,10 @@
         </is>
       </c>
       <c r="H99" t="n">
-        <v>26</v>
+        <v>25.38999938964844</v>
       </c>
       <c r="I99" t="n">
-        <v>1.692307692307692</v>
+        <v>1.732965776200015</v>
       </c>
       <c r="J99" t="n">
         <v>20</v>
@@ -5129,10 +5129,10 @@
         </is>
       </c>
       <c r="H100" t="n">
-        <v>1.080000042915344</v>
+        <v>1.059999942779541</v>
       </c>
       <c r="I100" t="n">
-        <v>2.77777766739881</v>
+        <v>2.830188832023306</v>
       </c>
       <c r="J100" t="n">
         <v>20</v>
@@ -5176,10 +5176,10 @@
         </is>
       </c>
       <c r="H101" t="n">
-        <v>8.520000457763672</v>
+        <v>8.470000267028809</v>
       </c>
       <c r="I101" t="n">
-        <v>5.516431628495071</v>
+        <v>5.548996283147359</v>
       </c>
       <c r="J101" t="n">
         <v>20</v>
@@ -5223,10 +5223,10 @@
         </is>
       </c>
       <c r="H102" t="n">
-        <v>54.52000045776367</v>
+        <v>53.58000183105469</v>
       </c>
       <c r="I102" t="n">
-        <v>2.567864982107936</v>
+        <v>2.612915177596294</v>
       </c>
       <c r="J102" t="n">
         <v>20</v>
@@ -5270,10 +5270,10 @@
         </is>
       </c>
       <c r="H103" t="n">
-        <v>3.878999948501587</v>
+        <v>3.858000040054321</v>
       </c>
       <c r="I103" t="n">
-        <v>7.733952152174854</v>
+        <v>7.776049685986419</v>
       </c>
       <c r="J103" t="n">
         <v>20</v>
@@ -5317,10 +5317,10 @@
         </is>
       </c>
       <c r="H104" t="n">
-        <v>11.94999980926514</v>
+        <v>12</v>
       </c>
       <c r="I104" t="n">
-        <v>1.004184116446269</v>
+        <v>1</v>
       </c>
       <c r="J104" t="n">
         <v>20</v>
@@ -5364,10 +5364,10 @@
         </is>
       </c>
       <c r="H105" t="n">
-        <v>3.569999933242798</v>
+        <v>3.559999942779541</v>
       </c>
       <c r="I105" t="n">
-        <v>4.761904850949985</v>
+        <v>4.775280975630273</v>
       </c>
       <c r="J105" t="n">
         <v>20</v>
@@ -5411,10 +5411,10 @@
         </is>
       </c>
       <c r="H106" t="n">
-        <v>20.95000076293945</v>
+        <v>20.85000038146973</v>
       </c>
       <c r="I106" t="n">
-        <v>3.341288661135993</v>
+        <v>3.357314087255938</v>
       </c>
       <c r="J106" t="n">
         <v>20</v>
@@ -5458,10 +5458,10 @@
         </is>
       </c>
       <c r="H107" t="n">
-        <v>2.700000047683716</v>
+        <v>2.599999904632568</v>
       </c>
       <c r="I107" t="n">
-        <v>1.29629627340288</v>
+        <v>1.346153895530477</v>
       </c>
       <c r="J107" t="n">
         <v>20</v>
@@ -5505,10 +5505,10 @@
         </is>
       </c>
       <c r="H108" t="n">
-        <v>6.190000057220459</v>
+        <v>6.130000114440918</v>
       </c>
       <c r="I108" t="n">
-        <v>5.331179272204762</v>
+        <v>5.383360421520929</v>
       </c>
       <c r="J108" t="n">
         <v>20</v>
@@ -5552,10 +5552,10 @@
         </is>
       </c>
       <c r="H109" t="n">
-        <v>0.9789999723434448</v>
+        <v>0.9929999709129333</v>
       </c>
       <c r="I109" t="n">
-        <v>7.15015341955936</v>
+        <v>7.049345624415697</v>
       </c>
       <c r="J109" t="n">
         <v>20</v>
@@ -5599,10 +5599,10 @@
         </is>
       </c>
       <c r="H110" t="n">
-        <v>49.63999938964844</v>
+        <v>49.81999969482422</v>
       </c>
       <c r="I110" t="n">
-        <v>1.430298164242238</v>
+        <v>1.42513047842062</v>
       </c>
       <c r="J110" t="n">
         <v>20</v>
@@ -5646,10 +5646,10 @@
         </is>
       </c>
       <c r="H111" t="n">
-        <v>90.75</v>
+        <v>92.5</v>
       </c>
       <c r="I111" t="n">
-        <v>1.487603305785124</v>
+        <v>1.459459459459459</v>
       </c>
       <c r="J111" t="n">
         <v>20</v>
@@ -5693,10 +5693,10 @@
         </is>
       </c>
       <c r="H112" t="n">
-        <v>7.179999828338623</v>
+        <v>7.199999809265137</v>
       </c>
       <c r="I112" t="n">
-        <v>1.114206154772446</v>
+        <v>1.111111140545505</v>
       </c>
       <c r="J112" t="n">
         <v>20</v>
@@ -5787,10 +5787,10 @@
         </is>
       </c>
       <c r="H114" t="n">
-        <v>4.533999919891357</v>
+        <v>4.585000038146973</v>
       </c>
       <c r="I114" t="n">
-        <v>3.749448676745312</v>
+        <v>3.707742608192115</v>
       </c>
       <c r="J114" t="n">
         <v>20</v>
@@ -5881,10 +5881,10 @@
         </is>
       </c>
       <c r="H116" t="n">
-        <v>59.70000076293945</v>
+        <v>58.40000152587891</v>
       </c>
       <c r="I116" t="n">
-        <v>0.753768834588275</v>
+        <v>0.7705479250725544</v>
       </c>
       <c r="J116" t="n">
         <v>20</v>
@@ -5928,10 +5928,10 @@
         </is>
       </c>
       <c r="H117" t="n">
-        <v>4.71999979019165</v>
+        <v>4.639999866485596</v>
       </c>
       <c r="I117" t="n">
-        <v>0.8474576647889183</v>
+        <v>0.8620689903229801</v>
       </c>
       <c r="J117" t="n">
         <v>20</v>
@@ -5975,10 +5975,10 @@
         </is>
       </c>
       <c r="H118" t="n">
-        <v>33.72000122070312</v>
+        <v>33.79999923706055</v>
       </c>
       <c r="I118" t="n">
-        <v>3.11387889083269</v>
+        <v>3.106508945860303</v>
       </c>
       <c r="J118" t="n">
         <v>20</v>
@@ -6069,10 +6069,10 @@
         </is>
       </c>
       <c r="H120" t="n">
-        <v>20.31999969482422</v>
+        <v>20.28000068664551</v>
       </c>
       <c r="I120" t="n">
-        <v>1.870078768243245</v>
+        <v>1.873767194940146</v>
       </c>
       <c r="J120" t="n">
         <v>20</v>
@@ -6116,10 +6116,10 @@
         </is>
       </c>
       <c r="H121" t="n">
-        <v>26.96999931335449</v>
+        <v>26.90999984741211</v>
       </c>
       <c r="I121" t="n">
-        <v>2.224694161200454</v>
+        <v>2.229654416210266</v>
       </c>
       <c r="J121" t="n">
         <v>20</v>
@@ -6163,10 +6163,10 @@
         </is>
       </c>
       <c r="H122" t="n">
-        <v>34.84999847412109</v>
+        <v>34.20000076293945</v>
       </c>
       <c r="I122" t="n">
-        <v>1.004304204661308</v>
+        <v>1.023391790035498</v>
       </c>
       <c r="J122" t="n">
         <v>20</v>
@@ -6210,10 +6210,10 @@
         </is>
       </c>
       <c r="H123" t="n">
-        <v>3.480000019073486</v>
+        <v>3.539999961853027</v>
       </c>
       <c r="I123" t="n">
-        <v>0.488505744448992</v>
+        <v>0.4802259938754712</v>
       </c>
       <c r="J123" t="n">
         <v>20</v>
@@ -6304,10 +6304,10 @@
         </is>
       </c>
       <c r="H125" t="n">
-        <v>22.3700008392334</v>
+        <v>22.23999977111816</v>
       </c>
       <c r="I125" t="n">
-        <v>5.006705221198291</v>
+        <v>5.035971274849027</v>
       </c>
       <c r="J125" t="n">
         <v>20</v>
@@ -6351,10 +6351,10 @@
         </is>
       </c>
       <c r="H126" t="n">
-        <v>1.490000009536743</v>
+        <v>1.470000028610229</v>
       </c>
       <c r="I126" t="n">
-        <v>6.711409353016787</v>
+        <v>6.802720956035778</v>
       </c>
       <c r="J126" t="n">
         <v>20</v>
@@ -6398,10 +6398,10 @@
         </is>
       </c>
       <c r="H127" t="n">
-        <v>2.519999980926514</v>
+        <v>2.51200008392334</v>
       </c>
       <c r="I127" t="n">
-        <v>10.31746039555156</v>
+        <v>10.35031812554408</v>
       </c>
       <c r="J127" t="n">
         <v>20</v>
@@ -6445,10 +6445,10 @@
         </is>
       </c>
       <c r="H128" t="n">
-        <v>2.323999881744385</v>
+        <v>2.328000068664551</v>
       </c>
       <c r="I128" t="n">
-        <v>3.971600890561147</v>
+        <v>3.964776515360997</v>
       </c>
       <c r="J128" t="n">
         <v>20</v>
@@ -6492,10 +6492,10 @@
         </is>
       </c>
       <c r="H129" t="n">
-        <v>9.600000381469727</v>
+        <v>9.279999732971191</v>
       </c>
       <c r="I129" t="n">
-        <v>3.645833188460938</v>
+        <v>3.771551832663038</v>
       </c>
       <c r="J129" t="n">
         <v>13</v>
@@ -6539,10 +6539,10 @@
         </is>
       </c>
       <c r="H130" t="n">
-        <v>5.550000190734863</v>
+        <v>5.400000095367432</v>
       </c>
       <c r="I130" t="n">
-        <v>1.729729670284729</v>
+        <v>1.777777746381093</v>
       </c>
       <c r="J130" t="n">
         <v>13</v>
@@ -6633,10 +6633,10 @@
         </is>
       </c>
       <c r="H132" t="n">
-        <v>11.80000019073486</v>
+        <v>11.69999980926514</v>
       </c>
       <c r="I132" t="n">
-        <v>1.694915226840727</v>
+        <v>1.70940173726859</v>
       </c>
       <c r="J132" t="n">
         <v>13</v>
@@ -6680,10 +6680,10 @@
         </is>
       </c>
       <c r="H133" t="n">
-        <v>9.220000267028809</v>
+        <v>9.380000114440918</v>
       </c>
       <c r="I133" t="n">
-        <v>0.6507592002417079</v>
+        <v>0.6396588408098992</v>
       </c>
       <c r="J133" t="n">
         <v>13</v>
@@ -6727,10 +6727,10 @@
         </is>
       </c>
       <c r="H134" t="n">
-        <v>2.259999990463257</v>
+        <v>2.220000028610229</v>
       </c>
       <c r="I134" t="n">
-        <v>2.654867267840171</v>
+        <v>2.702702667871647</v>
       </c>
       <c r="J134" t="n">
         <v>13</v>
@@ -6774,10 +6774,10 @@
         </is>
       </c>
       <c r="H135" t="n">
-        <v>16.28000068664551</v>
+        <v>16.31999969482422</v>
       </c>
       <c r="I135" t="n">
-        <v>3.071252941716091</v>
+        <v>3.063725547486203</v>
       </c>
       <c r="J135" t="n">
         <v>13</v>
@@ -6821,10 +6821,10 @@
         </is>
       </c>
       <c r="H136" t="n">
-        <v>4</v>
+        <v>4.019999980926514</v>
       </c>
       <c r="I136" t="n">
-        <v>2.5</v>
+        <v>2.487562200857334</v>
       </c>
       <c r="J136" t="n">
         <v>13</v>
@@ -6868,10 +6868,10 @@
         </is>
       </c>
       <c r="H137" t="n">
-        <v>3.160000085830688</v>
+        <v>3.299999952316284</v>
       </c>
       <c r="I137" t="n">
-        <v>3.481012563677942</v>
+        <v>3.333333381498703</v>
       </c>
       <c r="J137" t="n">
         <v>13</v>
@@ -7009,10 +7009,10 @@
         </is>
       </c>
       <c r="H140" t="n">
-        <v>1.299999952316284</v>
+        <v>1.259999990463257</v>
       </c>
       <c r="I140" t="n">
-        <v>2.30769239233796</v>
+        <v>2.380952398973438</v>
       </c>
       <c r="J140" t="n">
         <v>13</v>
@@ -7056,10 +7056,10 @@
         </is>
       </c>
       <c r="H141" t="n">
-        <v>7.699999809265137</v>
+        <v>7.599999904632568</v>
       </c>
       <c r="I141" t="n">
-        <v>1.168831197784008</v>
+        <v>1.184210541175673</v>
       </c>
       <c r="J141" t="n">
         <v>13</v>
@@ -7150,10 +7150,10 @@
         </is>
       </c>
       <c r="H143" t="n">
-        <v>7.03000020980835</v>
+        <v>7.070000171661377</v>
       </c>
       <c r="I143" t="n">
-        <v>3.129445141310993</v>
+        <v>3.11173966984929</v>
       </c>
       <c r="J143" t="n">
         <v>13</v>
@@ -7197,10 +7197,10 @@
         </is>
       </c>
       <c r="H144" t="n">
-        <v>25.85000038146973</v>
+        <v>26.54999923706055</v>
       </c>
       <c r="I144" t="n">
-        <v>2.359767856859575</v>
+        <v>2.297551855099546</v>
       </c>
       <c r="J144" t="n">
         <v>6</v>
@@ -7291,10 +7291,10 @@
         </is>
       </c>
       <c r="H146" t="n">
-        <v>12.35000038146973</v>
+        <v>12.19999980926514</v>
       </c>
       <c r="I146" t="n">
-        <v>5.668016019256961</v>
+        <v>5.737705007736096</v>
       </c>
       <c r="J146" t="n">
         <v>6</v>
@@ -7338,10 +7338,10 @@
         </is>
       </c>
       <c r="H147" t="n">
-        <v>9.279999732971191</v>
+        <v>9.239999771118164</v>
       </c>
       <c r="I147" t="n">
-        <v>5.501077744498517</v>
+        <v>5.524891911747554</v>
       </c>
       <c r="J147" t="n">
         <v>6</v>
@@ -7385,10 +7385,10 @@
         </is>
       </c>
       <c r="H148" t="n">
-        <v>7.724999904632568</v>
+        <v>7.715000152587891</v>
       </c>
       <c r="I148" t="n">
-        <v>3.495145674216579</v>
+        <v>3.499675886713136</v>
       </c>
       <c r="J148" t="n">
         <v>6</v>
@@ -7432,10 +7432,10 @@
         </is>
       </c>
       <c r="H149" t="n">
-        <v>5.769999980926514</v>
+        <v>5.71999979019165</v>
       </c>
       <c r="I149" t="n">
-        <v>6.065857905666734</v>
+        <v>6.118881343320349</v>
       </c>
       <c r="J149" t="n">
         <v>6</v>
@@ -7526,10 +7526,10 @@
         </is>
       </c>
       <c r="H151" t="n">
-        <v>19</v>
+        <v>18.89999961853027</v>
       </c>
       <c r="I151" t="n">
-        <v>3.947368421052631</v>
+        <v>3.968254048347555</v>
       </c>
       <c r="J151" t="n">
         <v>6</v>
@@ -7573,10 +7573,10 @@
         </is>
       </c>
       <c r="H152" t="n">
-        <v>11.69999980926514</v>
+        <v>11.55000019073486</v>
       </c>
       <c r="I152" t="n">
-        <v>3.675213735127469</v>
+        <v>3.722943661463623</v>
       </c>
       <c r="J152" t="n">
         <v>6</v>
@@ -7620,10 +7620,10 @@
         </is>
       </c>
       <c r="H153" t="n">
-        <v>4.28000020980835</v>
+        <v>4.260000228881836</v>
       </c>
       <c r="I153" t="n">
-        <v>3.504672725394953</v>
+        <v>3.521126571379833</v>
       </c>
       <c r="J153" t="n">
         <v>6</v>
@@ -7667,10 +7667,10 @@
         </is>
       </c>
       <c r="H154" t="n">
-        <v>12.68000030517578</v>
+        <v>12.5</v>
       </c>
       <c r="I154" t="n">
-        <v>1.554960530399346</v>
+        <v>1.577352</v>
       </c>
       <c r="J154" t="n">
         <v>6</v>
@@ -7714,10 +7714,10 @@
         </is>
       </c>
       <c r="H155" t="n">
-        <v>29.10000038146973</v>
+        <v>29.29999923706055</v>
       </c>
       <c r="I155" t="n">
-        <v>3.780068678969699</v>
+        <v>3.75426630936102</v>
       </c>
       <c r="J155" t="n">
         <v>6</v>
@@ -7761,10 +7761,10 @@
         </is>
       </c>
       <c r="H156" t="n">
-        <v>47.04999923706055</v>
+        <v>46.40000152587891</v>
       </c>
       <c r="I156" t="n">
-        <v>0.9989373169421614</v>
+        <v>1.012931001172197</v>
       </c>
       <c r="J156" t="n">
         <v>6</v>
@@ -7808,10 +7808,10 @@
         </is>
       </c>
       <c r="H157" t="n">
-        <v>80.69999694824219</v>
+        <v>79.09999847412109</v>
       </c>
       <c r="I157" t="n">
-        <v>1.486988903815737</v>
+        <v>1.517067033057656</v>
       </c>
       <c r="J157" t="n">
         <v>6</v>
@@ -7855,10 +7855,10 @@
         </is>
       </c>
       <c r="H158" t="n">
-        <v>23.75</v>
+        <v>24.29999923706055</v>
       </c>
       <c r="I158" t="n">
-        <v>1.136842105263158</v>
+        <v>1.111111145996318</v>
       </c>
       <c r="J158" t="n">
         <v>6</v>
@@ -7902,10 +7902,10 @@
         </is>
       </c>
       <c r="H159" t="n">
-        <v>10.55000019073486</v>
+        <v>10.44999980926514</v>
       </c>
       <c r="I159" t="n">
-        <v>3.601895669478002</v>
+        <v>3.636363702735056</v>
       </c>
       <c r="J159" t="n">
         <v>6</v>
@@ -7949,10 +7949,10 @@
         </is>
       </c>
       <c r="H160" t="n">
-        <v>29.70000076293945</v>
+        <v>29.54999923706055</v>
       </c>
       <c r="I160" t="n">
-        <v>1.010100984153337</v>
+        <v>1.01522845260771</v>
       </c>
       <c r="J160" t="n">
         <v>6</v>
@@ -7996,10 +7996,10 @@
         </is>
       </c>
       <c r="H161" t="n">
-        <v>0.1879999935626984</v>
+        <v>0.1824000030755997</v>
       </c>
       <c r="I161" t="n">
-        <v>3.723404382812112</v>
+        <v>3.837719233534605</v>
       </c>
       <c r="J161" t="n">
         <v>-1</v>
@@ -8043,10 +8043,10 @@
         </is>
       </c>
       <c r="H162" t="n">
-        <v>7.110000133514404</v>
+        <v>6.960000038146973</v>
       </c>
       <c r="I162" t="n">
-        <v>2.250351575182229</v>
+        <v>2.298850562112904</v>
       </c>
       <c r="J162" t="n">
         <v>-1</v>
@@ -8090,10 +8090,10 @@
         </is>
       </c>
       <c r="H163" t="n">
-        <v>2.184999942779541</v>
+        <v>2.190000057220459</v>
       </c>
       <c r="I163" t="n">
-        <v>2.974828453190412</v>
+        <v>2.968036452131321</v>
       </c>
       <c r="J163" t="n">
         <v>-1</v>
@@ -8137,10 +8137,10 @@
         </is>
       </c>
       <c r="H164" t="n">
-        <v>7.670000076293945</v>
+        <v>7.550000190734863</v>
       </c>
       <c r="I164" t="n">
-        <v>3.259452379572819</v>
+        <v>3.311258194493725</v>
       </c>
       <c r="J164" t="n">
         <v>-1</v>
@@ -8231,10 +8231,10 @@
         </is>
       </c>
       <c r="H166" t="n">
-        <v>6.559999942779541</v>
+        <v>6.570000171661377</v>
       </c>
       <c r="I166" t="n">
-        <v>7.621951285995664</v>
+        <v>7.610349877259797</v>
       </c>
       <c r="J166" t="n">
         <v>-8</v>
@@ -8278,10 +8278,10 @@
         </is>
       </c>
       <c r="H167" t="n">
-        <v>18.78499984741211</v>
+        <v>18.77499961853027</v>
       </c>
       <c r="I167" t="n">
-        <v>3.460207640563524</v>
+        <v>3.462050669542877</v>
       </c>
       <c r="J167" t="n">
         <v>-8</v>
@@ -8325,10 +8325,10 @@
         </is>
       </c>
       <c r="H168" t="n">
-        <v>12.55500030517578</v>
+        <v>12.47500038146973</v>
       </c>
       <c r="I168" t="n">
-        <v>4.301075164270492</v>
+        <v>4.328657182264395</v>
       </c>
       <c r="J168" t="n">
         <v>-8</v>
@@ -8372,10 +8372,10 @@
         </is>
       </c>
       <c r="H169" t="n">
-        <v>6.242000102996826</v>
+        <v>6.26800012588501</v>
       </c>
       <c r="I169" t="n">
-        <v>1.602050598364927</v>
+        <v>1.595405200887428</v>
       </c>
       <c r="J169" t="n">
         <v>-8</v>
@@ -8419,10 +8419,10 @@
         </is>
       </c>
       <c r="H170" t="n">
-        <v>9.380000114440918</v>
+        <v>9.180000305175781</v>
       </c>
       <c r="I170" t="n">
-        <v>1.705756908826398</v>
+        <v>1.742919332037389</v>
       </c>
       <c r="J170" t="n">
         <v>-8</v>
@@ -8466,10 +8466,10 @@
         </is>
       </c>
       <c r="H171" t="n">
-        <v>294.7999877929688</v>
+        <v>291.4500122070312</v>
       </c>
       <c r="I171" t="n">
-        <v>1.226255138971964</v>
+        <v>1.24034992231604</v>
       </c>
       <c r="J171" t="n">
         <v>-8</v>
@@ -8513,10 +8513,10 @@
         </is>
       </c>
       <c r="H172" t="n">
-        <v>30.5</v>
+        <v>30.29999923706055</v>
       </c>
       <c r="I172" t="n">
-        <v>4.459016393442623</v>
+        <v>4.488448957901479</v>
       </c>
       <c r="J172" t="n">
         <v>-8</v>
@@ -8560,10 +8560,10 @@
         </is>
       </c>
       <c r="H173" t="n">
-        <v>13.98999977111816</v>
+        <v>13.97999954223633</v>
       </c>
       <c r="I173" t="n">
-        <v>41.61258109537984</v>
+        <v>41.64234757241444</v>
       </c>
       <c r="J173" t="n">
         <v>-8</v>
@@ -8607,10 +8607,10 @@
         </is>
       </c>
       <c r="H174" t="n">
-        <v>14.72000026702881</v>
+        <v>14.63000011444092</v>
       </c>
       <c r="I174" t="n">
-        <v>3.974184710514823</v>
+        <v>3.998632914722678</v>
       </c>
       <c r="J174" t="n">
         <v>-8</v>
@@ -8654,10 +8654,10 @@
         </is>
       </c>
       <c r="H175" t="n">
-        <v>19.98500061035156</v>
+        <v>19.88500022888184</v>
       </c>
       <c r="I175" t="n">
-        <v>3.152364176930177</v>
+        <v>3.168217212715747</v>
       </c>
       <c r="J175" t="n">
         <v>-8</v>
@@ -8701,10 +8701,10 @@
         </is>
       </c>
       <c r="H176" t="n">
-        <v>125.4499969482422</v>
+        <v>123.1999969482422</v>
       </c>
       <c r="I176" t="n">
-        <v>0.7174173151804216</v>
+        <v>0.7305194986150048</v>
       </c>
       <c r="J176" t="n">
         <v>-8</v>
@@ -8748,10 +8748,10 @@
         </is>
       </c>
       <c r="H177" t="n">
-        <v>66.01000213623047</v>
+        <v>65.76999664306641</v>
       </c>
       <c r="I177" t="n">
-        <v>2.60687766143173</v>
+        <v>2.616390585115546</v>
       </c>
       <c r="J177" t="n">
         <v>-8</v>
@@ -8795,10 +8795,10 @@
         </is>
       </c>
       <c r="H178" t="n">
-        <v>25.79999923706055</v>
+        <v>25.89999961853027</v>
       </c>
       <c r="I178" t="n">
-        <v>0.5426356749611693</v>
+        <v>0.540540548501925</v>
       </c>
       <c r="J178" t="n">
         <v>-15</v>
@@ -8842,10 +8842,10 @@
         </is>
       </c>
       <c r="H179" t="n">
-        <v>1.580000042915344</v>
+        <v>1.570000052452087</v>
       </c>
       <c r="I179" t="n">
-        <v>3.797468251285027</v>
+        <v>3.821655923277815</v>
       </c>
       <c r="J179" t="n">
         <v>-15</v>
@@ -8889,10 +8889,10 @@
         </is>
       </c>
       <c r="H180" t="n">
-        <v>2.140000104904175</v>
+        <v>2.299999952316284</v>
       </c>
       <c r="I180" t="n">
-        <v>1.588784968845712</v>
+        <v>1.478260900212597</v>
       </c>
       <c r="J180" t="n">
         <v>-29</v>
@@ -9819,7 +9819,7 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>Xenia Hotellerie Solution S.p.A. Società Benefit</t>
+          <t>Vimi Fasteners S.p.A.</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -9836,7 +9836,7 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>YOLO GROUP S.p.A.</t>
+          <t>TradeLab S.p.A.</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -9853,7 +9853,7 @@
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>Xenia Hotellerie Solution S.p.A. Società Benefit</t>
+          <t>Unipol S.p.A.</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -9863,14 +9863,14 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>WIIT S.p.A.</t>
+          <t>WEBUILD S.p.A.</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -9887,7 +9887,7 @@
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>doxee S.p.A.</t>
+          <t>Toscana Aeroporti S.p.A.</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -10057,7 +10057,7 @@
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>WEBUILD S.p.A.</t>
+          <t>WIIT S.p.A.</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
@@ -10108,7 +10108,7 @@
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>Vimi Fasteners S.p.A.</t>
+          <t>Xenia Hotellerie Solution S.p.A. Società Benefit</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
@@ -10125,7 +10125,7 @@
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>RECORDATI S.p.A.</t>
+          <t>TXT E-SOLUTIONS S.p.A.</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
@@ -10142,7 +10142,7 @@
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>TradeLab S.p.A.</t>
+          <t>YOLO GROUP S.p.A.</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
@@ -10176,7 +10176,7 @@
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>TXT E-SOLUTIONS S.p.A.</t>
+          <t>Novamarine S.p.A.</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
@@ -10193,7 +10193,7 @@
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>TAMBURI INVESTMENT PARTNERS S.p.A.</t>
+          <t>PHILOGEN S.p.A.</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
@@ -10210,7 +10210,7 @@
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>T.P.S. S.p.A.</t>
+          <t>PLANETEL S.p.A.</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
@@ -10227,7 +10227,7 @@
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>Snam S.p.A.</t>
+          <t>PREMIA FINANCE S.P.A</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
@@ -10244,7 +10244,7 @@
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>SOSTRAVEL.COM S.p.A.</t>
+          <t>Pasquarelli Auto S.p.A.</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
@@ -10261,7 +10261,7 @@
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>SOGES GROUP S.p.A.</t>
+          <t>Porto Aviation Group S.p.A.</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
@@ -10278,7 +10278,7 @@
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>SABAF S.p.A.</t>
+          <t>Prysmian S.p.A.</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
@@ -10288,14 +10288,14 @@
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>Renovalo S.p.A.</t>
+          <t>RATTI S.p.A. SOCIETA' BENEFIT</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
@@ -10305,14 +10305,14 @@
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>Unipol S.p.A.</t>
+          <t>Xenia Hotellerie Solution S.p.A. Società Benefit</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
@@ -10322,14 +10322,14 @@
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>Redelfi S.p.A.</t>
+          <t>RECORDATI S.p.A.</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
@@ -10346,7 +10346,7 @@
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>RATTI S.p.A. SOCIETA' BENEFIT</t>
+          <t>TAMBURI INVESTMENT PARTNERS S.p.A.</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
@@ -10363,7 +10363,7 @@
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>Prysmian S.p.A.</t>
+          <t>T.P.S. S.p.A.</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
@@ -10373,14 +10373,14 @@
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>Porto Aviation Group S.p.A.</t>
+          <t>Snam S.p.A.</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
@@ -10397,7 +10397,7 @@
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>Pasquarelli Auto S.p.A.</t>
+          <t>SOSTRAVEL.COM S.p.A.</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
@@ -10414,7 +10414,7 @@
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>PREMIA FINANCE S.P.A</t>
+          <t>SOGES GROUP S.p.A.</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
@@ -10431,7 +10431,7 @@
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>PLANETEL S.p.A.</t>
+          <t>SABAF S.p.A.</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
@@ -10448,7 +10448,7 @@
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>PHILOGEN S.p.A.</t>
+          <t>Renovalo S.p.A.</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
@@ -10458,14 +10458,14 @@
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>Novamarine S.p.A.</t>
+          <t>Redelfi S.p.A.</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
@@ -10482,7 +10482,7 @@
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>Toscana Aeroporti S.p.A.</t>
+          <t>RedFish LongTerm Capital S.p.A.</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
@@ -10533,7 +10533,7 @@
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>RedFish LongTerm Capital S.p.A.</t>
+          <t>doxee S.p.A.</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
@@ -10567,7 +10567,7 @@
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>E.P.H. S.p.A.</t>
+          <t>ELICA S.p.A.</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
@@ -10577,14 +10577,14 @@
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>Bod Annual Report</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>E-Globe S.p.A.</t>
+          <t>ELICA S.p.A.</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
@@ -10594,14 +10594,14 @@
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>Bod Annual Report</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>DiaSorin S.p.A</t>
+          <t>EL.EN. S.p.A.</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
@@ -10618,7 +10618,7 @@
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>Datrix S.p.A.</t>
+          <t>E.P.H. S.p.A.</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
@@ -10628,14 +10628,14 @@
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Bod Annual Report</t>
         </is>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>DHH S.p.A.</t>
+          <t>E-Globe S.p.A.</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
@@ -10645,14 +10645,14 @@
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Bod Annual Report</t>
         </is>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>DEA CAPITAL REAL ESTATE SGR S.p.A.</t>
+          <t>DiaSorin S.p.A</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
@@ -10662,14 +10662,14 @@
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>D'AMICO INTERNATIONAL SHIPPING S.A.</t>
+          <t>Datrix S.p.A.</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
@@ -10686,7 +10686,7 @@
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>Cloudia Research S.p.A.</t>
+          <t>DHH S.p.A.</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
@@ -10696,14 +10696,14 @@
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>Bod Annual Report</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>CREDITO EMILIANO S.p.A.</t>
+          <t>DEA CAPITAL REAL ESTATE SGR S.p.A.</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
@@ -10713,14 +10713,14 @@
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>CONVERGENZE S.p.A. SOCIETA' BENEFIT</t>
+          <t>D'AMICO INTERNATIONAL SHIPPING S.A.</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
@@ -10737,7 +10737,7 @@
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>CIRCLE S.p.A.</t>
+          <t>Cloudia Research S.p.A.</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
@@ -10747,14 +10747,14 @@
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Bod Annual Report</t>
         </is>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>EL.EN. S.p.A.</t>
+          <t>CREDITO EMILIANO S.p.A.</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
@@ -10771,7 +10771,7 @@
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>CEMBRE S.p.A.</t>
+          <t>CONVERGENZE S.p.A. SOCIETA' BENEFIT</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
@@ -10788,7 +10788,7 @@
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>Bellini Nautica S.p.A.</t>
+          <t>CIRCLE S.p.A.</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
@@ -10805,7 +10805,7 @@
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>BREMBO N.V.</t>
+          <t>Iniziative Bresciane - INBRE - S.p.A.</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
@@ -10822,7 +10822,7 @@
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>BIESSE S.p.A.</t>
+          <t>BolognaFiere S.p.A.</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
@@ -10839,7 +10839,7 @@
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>BEEWIZE</t>
+          <t>Bellini Nautica S.p.A.</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
@@ -10849,14 +10849,14 @@
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>Bod Annual Report</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>BANCO DI DESIO E DELLA BRIANZA S.p.A.</t>
+          <t>BREMBO N.V.</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
@@ -10873,7 +10873,7 @@
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>B&amp;C SPEAKERS S.p.A.</t>
+          <t>BIESSE S.p.A.</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
@@ -10890,7 +10890,7 @@
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>Arterra Bioscience S.p.A.</t>
+          <t>BEEWIZE</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
@@ -10900,14 +10900,14 @@
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Bod Annual Report</t>
         </is>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>Ambromobiliare S.p.A.</t>
+          <t>BANCO DI DESIO E DELLA BRIANZA S.p.A.</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
@@ -10924,7 +10924,7 @@
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>ABC Company S.p.A. Società Benefit</t>
+          <t>B&amp;C SPEAKERS S.p.A.</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
@@ -10941,7 +10941,7 @@
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>A2A S.p.A.</t>
+          <t>Arterra Bioscience S.p.A.</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
@@ -10958,7 +10958,7 @@
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>Confinvest Oro S.p.A.</t>
+          <t>Ambromobiliare S.p.A.</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
@@ -10975,7 +10975,7 @@
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>BolognaFiere S.p.A.</t>
+          <t>ABC Company S.p.A. Società Benefit</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
@@ -10992,7 +10992,7 @@
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>ELICA S.p.A.</t>
+          <t>A2A S.p.A.</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
@@ -11009,7 +11009,7 @@
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>Iniziative Bresciane - INBRE - S.p.A.</t>
+          <t>Confinvest Oro S.p.A.</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
@@ -11043,7 +11043,7 @@
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>FinecoBank S.p.A.</t>
+          <t>ENA S.p.A.</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
@@ -11060,7 +11060,7 @@
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>G.M. Leather S.p.A.</t>
+          <t>CEMBRE S.p.A.</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
@@ -11077,7 +11077,7 @@
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>GPI S.p.A.</t>
+          <t>HERA S.p.A.</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
@@ -11094,7 +11094,7 @@
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>Gentili Mosconi S.p.A.</t>
+          <t>Energy S.p.A.</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
@@ -11111,7 +11111,7 @@
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>Giglio.com S.p.A.</t>
+          <t>EdgeLab S.p.A.</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
@@ -11128,7 +11128,7 @@
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>F.I.L.A. S.p.A.</t>
+          <t>EUROTECH S.p.A.</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
@@ -11145,7 +11145,7 @@
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>Energy S.p.A.</t>
+          <t>EUKEDOS S.p.A.</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
@@ -11162,7 +11162,7 @@
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>EdgeLab S.p.A.</t>
+          <t>F.I.L.A. S.p.A.</t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
@@ -11179,7 +11179,7 @@
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>EUROTECH S.p.A.</t>
+          <t>FinecoBank S.p.A.</t>
         </is>
       </c>
       <c r="B134" t="inlineStr">
@@ -11196,7 +11196,7 @@
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>HELYX INDUSTRIES S.p.A.</t>
+          <t>G.M. Leather S.p.A.</t>
         </is>
       </c>
       <c r="B135" t="inlineStr">
@@ -11213,7 +11213,7 @@
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t>EUKEDOS S.p.A.</t>
+          <t>Gentili Mosconi S.p.A.</t>
         </is>
       </c>
       <c r="B136" t="inlineStr">
@@ -11230,7 +11230,7 @@
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t>HIGH QUALITY FOOD S.p.A.</t>
+          <t>Giglio.com S.p.A.</t>
         </is>
       </c>
       <c r="B137" t="inlineStr">
@@ -11240,14 +11240,14 @@
       </c>
       <c r="C137" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t>ITALIAN EXHIBITION GROUP S.p.A.</t>
+          <t>HELYX INDUSTRIES S.p.A.</t>
         </is>
       </c>
       <c r="B138" t="inlineStr">
@@ -11264,7 +11264,7 @@
     <row r="139">
       <c r="A139" t="inlineStr">
         <is>
-          <t>ELICA S.p.A.</t>
+          <t>GPI S.p.A.</t>
         </is>
       </c>
       <c r="B139" t="inlineStr">
@@ -11274,14 +11274,14 @@
       </c>
       <c r="C139" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="140">
       <c r="A140" t="inlineStr">
         <is>
-          <t>ENA S.p.A.</t>
+          <t>ITALIAN EXHIBITION GROUP S.p.A.</t>
         </is>
       </c>
       <c r="B140" t="inlineStr">
@@ -11298,7 +11298,7 @@
     <row r="141">
       <c r="A141" t="inlineStr">
         <is>
-          <t>HERA S.p.A.</t>
+          <t>HIGH QUALITY FOOD S.p.A.</t>
         </is>
       </c>
       <c r="B141" t="inlineStr">
@@ -11308,14 +11308,14 @@
       </c>
       <c r="C141" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="142">
       <c r="A142" t="inlineStr">
         <is>
-          <t>Lucisano Media Group S.p.A.</t>
+          <t>Softlab S.p.A.</t>
         </is>
       </c>
       <c r="B142" t="inlineStr">
@@ -11325,14 +11325,14 @@
       </c>
       <c r="C142" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Bod Annual Report</t>
         </is>
       </c>
     </row>
     <row r="143">
       <c r="A143" t="inlineStr">
         <is>
-          <t>Itway S.p.A.</t>
+          <t>Società Editoriale il Fatto S.p.A.</t>
         </is>
       </c>
       <c r="B143" t="inlineStr">
@@ -11342,14 +11342,14 @@
       </c>
       <c r="C143" t="inlineStr">
         <is>
-          <t>Bod Annual Report</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="144">
       <c r="A144" t="inlineStr">
         <is>
-          <t>Italian Wine Brands S.p.A.</t>
+          <t>Saccheria F.lli Franceschetti S.p.A.</t>
         </is>
       </c>
       <c r="B144" t="inlineStr">
@@ -11366,7 +11366,7 @@
     <row r="145">
       <c r="A145" t="inlineStr">
         <is>
-          <t>Intesa Sanpaolo S.p.A.</t>
+          <t>STAR7 S.p.A.</t>
         </is>
       </c>
       <c r="B145" t="inlineStr">
@@ -11383,7 +11383,7 @@
     <row r="146">
       <c r="A146" t="inlineStr">
         <is>
-          <t>Iniziative Bresciane - INBRE - S.p.A.</t>
+          <t>INNOVATEC S.p.A.</t>
         </is>
       </c>
       <c r="B146" t="inlineStr">
@@ -11400,7 +11400,7 @@
     <row r="147">
       <c r="A147" t="inlineStr">
         <is>
-          <t>IRCE s.p.a</t>
+          <t>INTERPUMP GROUP S.p.A.</t>
         </is>
       </c>
       <c r="B147" t="inlineStr">
@@ -11417,7 +11417,7 @@
     <row r="148">
       <c r="A148" t="inlineStr">
         <is>
-          <t>Litix S.p.A.</t>
+          <t>INWIT S.p.A.</t>
         </is>
       </c>
       <c r="B148" t="inlineStr">
@@ -11434,7 +11434,7 @@
     <row r="149">
       <c r="A149" t="inlineStr">
         <is>
-          <t>E.T.S. S.p.A. Engineering and Technical Services</t>
+          <t>IRCE s.p.a</t>
         </is>
       </c>
       <c r="B149" t="inlineStr">
@@ -11451,7 +11451,7 @@
     <row r="150">
       <c r="A150" t="inlineStr">
         <is>
-          <t>Energy S.p.A.</t>
+          <t>Intesa Sanpaolo S.p.A.</t>
         </is>
       </c>
       <c r="B150" t="inlineStr">
@@ -11468,7 +11468,7 @@
     <row r="151">
       <c r="A151" t="inlineStr">
         <is>
-          <t>Emma Villas S.p.A.</t>
+          <t>SOSTRAVEL.COM S.p.A.</t>
         </is>
       </c>
       <c r="B151" t="inlineStr">
@@ -11485,7 +11485,7 @@
     <row r="152">
       <c r="A152" t="inlineStr">
         <is>
-          <t>Solid World Group S.p.A.</t>
+          <t>SOGES GROUP S.p.A.</t>
         </is>
       </c>
       <c r="B152" t="inlineStr">
@@ -11502,7 +11502,7 @@
     <row r="153">
       <c r="A153" t="inlineStr">
         <is>
-          <t>Softlab S.p.A.</t>
+          <t>SBE-Varvit S.p.A.</t>
         </is>
       </c>
       <c r="B153" t="inlineStr">
@@ -11512,14 +11512,14 @@
       </c>
       <c r="C153" t="inlineStr">
         <is>
-          <t>Bod Annual Report</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="154">
       <c r="A154" t="inlineStr">
         <is>
-          <t>Società Editoriale il Fatto S.p.A.</t>
+          <t>GAROFALO HEALTH CARE S.p.A.</t>
         </is>
       </c>
       <c r="B154" t="inlineStr">
@@ -11536,7 +11536,7 @@
     <row r="155">
       <c r="A155" t="inlineStr">
         <is>
-          <t>Saccheria F.lli Franceschetti S.p.A.</t>
+          <t>Reway Group S.p.A.</t>
         </is>
       </c>
       <c r="B155" t="inlineStr">
@@ -11553,7 +11553,7 @@
     <row r="156">
       <c r="A156" t="inlineStr">
         <is>
-          <t>STAR7 S.p.A.</t>
+          <t>Iniziative Bresciane - INBRE - S.p.A.</t>
         </is>
       </c>
       <c r="B156" t="inlineStr">
@@ -11570,7 +11570,7 @@
     <row r="157">
       <c r="A157" t="inlineStr">
         <is>
-          <t>SOSTRAVEL.COM S.p.A.</t>
+          <t>GEL S.p.A.</t>
         </is>
       </c>
       <c r="B157" t="inlineStr">
@@ -11587,7 +11587,7 @@
     <row r="158">
       <c r="A158" t="inlineStr">
         <is>
-          <t>SOGES GROUP S.p.A.</t>
+          <t>WEBSOLUTE S.p.A.</t>
         </is>
       </c>
       <c r="B158" t="inlineStr">
@@ -11604,7 +11604,7 @@
     <row r="159">
       <c r="A159" t="inlineStr">
         <is>
-          <t>ESI S.p.A.</t>
+          <t>Gabetti Property Solutions S.p.A.</t>
         </is>
       </c>
       <c r="B159" t="inlineStr">
@@ -11621,7 +11621,7 @@
     <row r="160">
       <c r="A160" t="inlineStr">
         <is>
-          <t>SBE-Varvit S.p.A.</t>
+          <t>iVision Tech S.p.A.</t>
         </is>
       </c>
       <c r="B160" t="inlineStr">
@@ -11638,7 +11638,7 @@
     <row r="161">
       <c r="A161" t="inlineStr">
         <is>
-          <t>First Capital S.p.A.</t>
+          <t>doxee S.p.A.</t>
         </is>
       </c>
       <c r="B161" t="inlineStr">
@@ -11655,7 +11655,7 @@
     <row r="162">
       <c r="A162" t="inlineStr">
         <is>
-          <t>FRANCHETTI S.p.A.</t>
+          <t>Redelfi S.p.A.</t>
         </is>
       </c>
       <c r="B162" t="inlineStr">
@@ -11672,7 +11672,7 @@
     <row r="163">
       <c r="A163" t="inlineStr">
         <is>
-          <t>FAE Technology Società Benefit S.p.A.</t>
+          <t>RedFish LongTerm Capital S.p.A.</t>
         </is>
       </c>
       <c r="B163" t="inlineStr">
@@ -11682,14 +11682,14 @@
       </c>
       <c r="C163" t="inlineStr">
         <is>
-          <t>Bod Annual Report</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="164">
       <c r="A164" t="inlineStr">
         <is>
-          <t>Execus S.p.A.</t>
+          <t>ROSETTI MARINO S.p.A.</t>
         </is>
       </c>
       <c r="B164" t="inlineStr">
@@ -11706,7 +11706,7 @@
     <row r="165">
       <c r="A165" t="inlineStr">
         <is>
-          <t>ErreDue S.p.A.</t>
+          <t>Prysmian S.p.A.</t>
         </is>
       </c>
       <c r="B165" t="inlineStr">
@@ -11716,14 +11716,14 @@
       </c>
       <c r="C165" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="166">
       <c r="A166" t="inlineStr">
         <is>
-          <t>Eprcomunicazione S.p.A. Società Benefit</t>
+          <t>Pozzi Milano S.p.A.</t>
         </is>
       </c>
       <c r="B166" t="inlineStr">
@@ -11740,7 +11740,7 @@
     <row r="167">
       <c r="A167" t="inlineStr">
         <is>
-          <t>INWIT S.p.A.</t>
+          <t>PREMIA FINANCE S.P.A</t>
         </is>
       </c>
       <c r="B167" t="inlineStr">
@@ -11757,7 +11757,7 @@
     <row r="168">
       <c r="A168" t="inlineStr">
         <is>
-          <t>Reway Group S.p.A.</t>
+          <t>PLC S.p.A.</t>
         </is>
       </c>
       <c r="B168" t="inlineStr">
@@ -11774,7 +11774,7 @@
     <row r="169">
       <c r="A169" t="inlineStr">
         <is>
-          <t>INTERPUMP GROUP S.p.A.</t>
+          <t>Next Geosolutions Europe S.p.A.</t>
         </is>
       </c>
       <c r="B169" t="inlineStr">
@@ -11791,7 +11791,7 @@
     <row r="170">
       <c r="A170" t="inlineStr">
         <is>
-          <t>TAMBURI INVESTMENT PARTNERS S.p.A.</t>
+          <t>Maps S.p.A.</t>
         </is>
       </c>
       <c r="B170" t="inlineStr">
@@ -11808,7 +11808,7 @@
     <row r="171">
       <c r="A171" t="inlineStr">
         <is>
-          <t>Vimi Fasteners S.p.A.</t>
+          <t>MARE ENGINEERING GROUP S.p.A.</t>
         </is>
       </c>
       <c r="B171" t="inlineStr">
@@ -11825,7 +11825,7 @@
     <row r="172">
       <c r="A172" t="inlineStr">
         <is>
-          <t>Maps S.p.A.</t>
+          <t>CEMBRE S.p.A.</t>
         </is>
       </c>
       <c r="B172" t="inlineStr">
@@ -11842,7 +11842,7 @@
     <row r="173">
       <c r="A173" t="inlineStr">
         <is>
-          <t>MARE ENGINEERING GROUP S.p.A.</t>
+          <t>Solid World Group S.p.A.</t>
         </is>
       </c>
       <c r="B173" t="inlineStr">
@@ -11859,7 +11859,7 @@
     <row r="174">
       <c r="A174" t="inlineStr">
         <is>
-          <t>CELLULARLINE S.p.A.</t>
+          <t>CONVERGENZE S.p.A. SOCIETA' BENEFIT</t>
         </is>
       </c>
       <c r="B174" t="inlineStr">
@@ -11876,7 +11876,7 @@
     <row r="175">
       <c r="A175" t="inlineStr">
         <is>
-          <t>Basic Net S.p.A.</t>
+          <t>CleanBnB S.p.A.</t>
         </is>
       </c>
       <c r="B175" t="inlineStr">
@@ -11886,14 +11886,14 @@
       </c>
       <c r="C175" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="176">
       <c r="A176" t="inlineStr">
         <is>
-          <t>Basic Net S.p.A.</t>
+          <t>Com.Tel S.p.A.</t>
         </is>
       </c>
       <c r="B176" t="inlineStr">
@@ -11903,14 +11903,14 @@
       </c>
       <c r="C176" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="177">
       <c r="A177" t="inlineStr">
         <is>
-          <t>BFF Bank S.P.A.</t>
+          <t>Copernico SIM S.p.A.</t>
         </is>
       </c>
       <c r="B177" t="inlineStr">
@@ -11920,14 +11920,14 @@
       </c>
       <c r="C177" t="inlineStr">
         <is>
-          <t>Bod Annual Report</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="178">
       <c r="A178" t="inlineStr">
         <is>
-          <t>BANCO DI DESIO E DELLA BRIANZA S.p.A.</t>
+          <t>DHH S.p.A.</t>
         </is>
       </c>
       <c r="B178" t="inlineStr">
@@ -11944,7 +11944,7 @@
     <row r="179">
       <c r="A179" t="inlineStr">
         <is>
-          <t>Arterra Bioscience S.p.A.</t>
+          <t>Datrix S.p.A.</t>
         </is>
       </c>
       <c r="B179" t="inlineStr">
@@ -11961,7 +11961,7 @@
     <row r="180">
       <c r="A180" t="inlineStr">
         <is>
-          <t>Alfio Bardolla Training Group S.p.A.</t>
+          <t>DigiTouch S.p.A.</t>
         </is>
       </c>
       <c r="B180" t="inlineStr">
@@ -11978,7 +11978,7 @@
     <row r="181">
       <c r="A181" t="inlineStr">
         <is>
-          <t>ACQUAZZURRA S.p.A.</t>
+          <t>Distribuzione Elettrica Adriatica S.p.A.</t>
         </is>
       </c>
       <c r="B181" t="inlineStr">
@@ -11995,7 +11995,7 @@
     <row r="182">
       <c r="A182" t="inlineStr">
         <is>
-          <t>Next Geosolutions Europe S.p.A.</t>
+          <t>IMMSI S.p.A.</t>
         </is>
       </c>
       <c r="B182" t="inlineStr">
@@ -12012,7 +12012,7 @@
     <row r="183">
       <c r="A183" t="inlineStr">
         <is>
-          <t>PLC S.p.A.</t>
+          <t>ILPRA S.p.A.</t>
         </is>
       </c>
       <c r="B183" t="inlineStr">
@@ -12029,7 +12029,7 @@
     <row r="184">
       <c r="A184" t="inlineStr">
         <is>
-          <t>INNOVATEC S.p.A.</t>
+          <t>Haiki+ S.p.A.</t>
         </is>
       </c>
       <c r="B184" t="inlineStr">
@@ -12046,7 +12046,7 @@
     <row r="185">
       <c r="A185" t="inlineStr">
         <is>
-          <t>PREMIA FINANCE S.P.A</t>
+          <t>HIGH QUALITY FOOD S.p.A.</t>
         </is>
       </c>
       <c r="B185" t="inlineStr">
@@ -12063,7 +12063,7 @@
     <row r="186">
       <c r="A186" t="inlineStr">
         <is>
-          <t>Prysmian S.p.A.</t>
+          <t>Gismondi 1754 S.p.A.</t>
         </is>
       </c>
       <c r="B186" t="inlineStr">
@@ -12073,14 +12073,14 @@
       </c>
       <c r="C186" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="187">
       <c r="A187" t="inlineStr">
         <is>
-          <t>ROSETTI MARINO S.p.A.</t>
+          <t>Gentili Mosconi S.p.A.</t>
         </is>
       </c>
       <c r="B187" t="inlineStr">
@@ -12097,7 +12097,7 @@
     <row r="188">
       <c r="A188" t="inlineStr">
         <is>
-          <t>Somec S.p.A.</t>
+          <t>CROWDFUNDME S.p.A.</t>
         </is>
       </c>
       <c r="B188" t="inlineStr">
@@ -12107,14 +12107,14 @@
       </c>
       <c r="C188" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Bod Annual Report</t>
         </is>
       </c>
     </row>
     <row r="189">
       <c r="A189" t="inlineStr">
         <is>
-          <t>Redelfi S.p.A.</t>
+          <t>Somec S.p.A.</t>
         </is>
       </c>
       <c r="B189" t="inlineStr">
@@ -12131,7 +12131,7 @@
     <row r="190">
       <c r="A190" t="inlineStr">
         <is>
-          <t>Stellantis N.V.</t>
+          <t>GREEN OLEO S.p.A</t>
         </is>
       </c>
       <c r="B190" t="inlineStr">
@@ -12141,14 +12141,14 @@
       </c>
       <c r="C190" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="191">
       <c r="A191" t="inlineStr">
         <is>
-          <t>Stellantis N.V.</t>
+          <t>Eprcomunicazione S.p.A. Società Benefit</t>
         </is>
       </c>
       <c r="B191" t="inlineStr">
@@ -12158,14 +12158,14 @@
       </c>
       <c r="C191" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="192">
       <c r="A192" t="inlineStr">
         <is>
-          <t>T.P.S. S.p.A.</t>
+          <t>FAE Technology Società Benefit S.p.A.</t>
         </is>
       </c>
       <c r="B192" t="inlineStr">
@@ -12175,14 +12175,14 @@
       </c>
       <c r="C192" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Bod Annual Report</t>
         </is>
       </c>
     </row>
     <row r="193">
       <c r="A193" t="inlineStr">
         <is>
-          <t>TMP Group S.p.A.</t>
+          <t>AATECH S.p.A. Società Benefit</t>
         </is>
       </c>
       <c r="B193" t="inlineStr">
@@ -12192,14 +12192,14 @@
       </c>
       <c r="C193" t="inlineStr">
         <is>
-          <t>Bod Annual Report</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="194">
       <c r="A194" t="inlineStr">
         <is>
-          <t>Tecno S.p.A. Società Benefit</t>
+          <t>E.T.S. S.p.A. Engineering and Technical Services</t>
         </is>
       </c>
       <c r="B194" t="inlineStr">
@@ -12216,7 +12216,7 @@
     <row r="195">
       <c r="A195" t="inlineStr">
         <is>
-          <t>UCapital24 S.p.A.</t>
+          <t>Vimi Fasteners S.p.A.</t>
         </is>
       </c>
       <c r="B195" t="inlineStr">
@@ -12233,7 +12233,7 @@
     <row r="196">
       <c r="A196" t="inlineStr">
         <is>
-          <t>VALTECNE S.p.A.</t>
+          <t>Valica S.p.A.</t>
         </is>
       </c>
       <c r="B196" t="inlineStr">
@@ -12250,7 +12250,7 @@
     <row r="197">
       <c r="A197" t="inlineStr">
         <is>
-          <t>Valica S.p.A.</t>
+          <t>VALTECNE S.p.A.</t>
         </is>
       </c>
       <c r="B197" t="inlineStr">
@@ -12267,7 +12267,7 @@
     <row r="198">
       <c r="A198" t="inlineStr">
         <is>
-          <t>Pozzi Milano S.p.A.</t>
+          <t>UCapital24 S.p.A.</t>
         </is>
       </c>
       <c r="B198" t="inlineStr">
@@ -12284,7 +12284,7 @@
     <row r="199">
       <c r="A199" t="inlineStr">
         <is>
-          <t>RedFish LongTerm Capital S.p.A.</t>
+          <t>Tecno S.p.A. Società Benefit</t>
         </is>
       </c>
       <c r="B199" t="inlineStr">
@@ -12301,7 +12301,7 @@
     <row r="200">
       <c r="A200" t="inlineStr">
         <is>
-          <t>AATECH S.p.A. Società Benefit</t>
+          <t>TMP Group S.p.A.</t>
         </is>
       </c>
       <c r="B200" t="inlineStr">
@@ -12311,14 +12311,14 @@
       </c>
       <c r="C200" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Bod Annual Report</t>
         </is>
       </c>
     </row>
     <row r="201">
       <c r="A201" t="inlineStr">
         <is>
-          <t>DHH S.p.A.</t>
+          <t>TAMBURI INVESTMENT PARTNERS S.p.A.</t>
         </is>
       </c>
       <c r="B201" t="inlineStr">
@@ -12335,7 +12335,7 @@
     <row r="202">
       <c r="A202" t="inlineStr">
         <is>
-          <t>Datrix S.p.A.</t>
+          <t>T.P.S. S.p.A.</t>
         </is>
       </c>
       <c r="B202" t="inlineStr">
@@ -12352,7 +12352,7 @@
     <row r="203">
       <c r="A203" t="inlineStr">
         <is>
-          <t>Distribuzione Elettrica Adriatica S.p.A.</t>
+          <t>Stellantis N.V.</t>
         </is>
       </c>
       <c r="B203" t="inlineStr">
@@ -12362,14 +12362,14 @@
       </c>
       <c r="C203" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="204">
       <c r="A204" t="inlineStr">
         <is>
-          <t>DigiTouch S.p.A.</t>
+          <t>Stellantis N.V.</t>
         </is>
       </c>
       <c r="B204" t="inlineStr">
@@ -12379,14 +12379,14 @@
       </c>
       <c r="C204" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="205">
       <c r="A205" t="inlineStr">
         <is>
-          <t>ABC Company S.p.A. Società Benefit</t>
+          <t>ESI S.p.A.</t>
         </is>
       </c>
       <c r="B205" t="inlineStr">
@@ -12403,7 +12403,7 @@
     <row r="206">
       <c r="A206" t="inlineStr">
         <is>
-          <t>iVision Tech S.p.A.</t>
+          <t>Emma Villas S.p.A.</t>
         </is>
       </c>
       <c r="B206" t="inlineStr">
@@ -12420,7 +12420,7 @@
     <row r="207">
       <c r="A207" t="inlineStr">
         <is>
-          <t>doxee S.p.A.</t>
+          <t>Energy S.p.A.</t>
         </is>
       </c>
       <c r="B207" t="inlineStr">
@@ -12437,7 +12437,7 @@
     <row r="208">
       <c r="A208" t="inlineStr">
         <is>
-          <t>WEBSOLUTE S.p.A.</t>
+          <t>First Capital S.p.A.</t>
         </is>
       </c>
       <c r="B208" t="inlineStr">
@@ -12454,7 +12454,7 @@
     <row r="209">
       <c r="A209" t="inlineStr">
         <is>
-          <t>IMMSI S.p.A.</t>
+          <t>ErreDue S.p.A.</t>
         </is>
       </c>
       <c r="B209" t="inlineStr">
@@ -12471,7 +12471,7 @@
     <row r="210">
       <c r="A210" t="inlineStr">
         <is>
-          <t>ILPRA S.p.A.</t>
+          <t>Execus S.p.A.</t>
         </is>
       </c>
       <c r="B210" t="inlineStr">
@@ -12488,7 +12488,7 @@
     <row r="211">
       <c r="A211" t="inlineStr">
         <is>
-          <t>Haiki+ S.p.A.</t>
+          <t>Litix S.p.A.</t>
         </is>
       </c>
       <c r="B211" t="inlineStr">
@@ -12505,7 +12505,7 @@
     <row r="212">
       <c r="A212" t="inlineStr">
         <is>
-          <t>HIGH QUALITY FOOD S.p.A.</t>
+          <t>Itway S.p.A.</t>
         </is>
       </c>
       <c r="B212" t="inlineStr">
@@ -12515,14 +12515,14 @@
       </c>
       <c r="C212" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Bod Annual Report</t>
         </is>
       </c>
     </row>
     <row r="213">
       <c r="A213" t="inlineStr">
         <is>
-          <t>Gismondi 1754 S.p.A.</t>
+          <t>Lucisano Media Group S.p.A.</t>
         </is>
       </c>
       <c r="B213" t="inlineStr">
@@ -12539,7 +12539,7 @@
     <row r="214">
       <c r="A214" t="inlineStr">
         <is>
-          <t>Gentili Mosconi S.p.A.</t>
+          <t>Alfio Bardolla Training Group S.p.A.</t>
         </is>
       </c>
       <c r="B214" t="inlineStr">
@@ -12556,7 +12556,7 @@
     <row r="215">
       <c r="A215" t="inlineStr">
         <is>
-          <t>Gabetti Property Solutions S.p.A.</t>
+          <t>CELLULARLINE S.p.A.</t>
         </is>
       </c>
       <c r="B215" t="inlineStr">
@@ -12573,7 +12573,7 @@
     <row r="216">
       <c r="A216" t="inlineStr">
         <is>
-          <t>Copernico SIM S.p.A.</t>
+          <t>Basic Net S.p.A.</t>
         </is>
       </c>
       <c r="B216" t="inlineStr">
@@ -12583,14 +12583,14 @@
       </c>
       <c r="C216" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="217">
       <c r="A217" t="inlineStr">
         <is>
-          <t>CEMBRE S.p.A.</t>
+          <t>Basic Net S.p.A.</t>
         </is>
       </c>
       <c r="B217" t="inlineStr">
@@ -12600,14 +12600,14 @@
       </c>
       <c r="C217" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="218">
       <c r="A218" t="inlineStr">
         <is>
-          <t>CONVERGENZE S.p.A. SOCIETA' BENEFIT</t>
+          <t>BFF Bank S.P.A.</t>
         </is>
       </c>
       <c r="B218" t="inlineStr">
@@ -12617,14 +12617,14 @@
       </c>
       <c r="C218" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Bod Annual Report</t>
         </is>
       </c>
     </row>
     <row r="219">
       <c r="A219" t="inlineStr">
         <is>
-          <t>CROWDFUNDME S.p.A.</t>
+          <t>BANCO DI DESIO E DELLA BRIANZA S.p.A.</t>
         </is>
       </c>
       <c r="B219" t="inlineStr">
@@ -12634,14 +12634,14 @@
       </c>
       <c r="C219" t="inlineStr">
         <is>
-          <t>Bod Annual Report</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="220">
       <c r="A220" t="inlineStr">
         <is>
-          <t>CleanBnB S.p.A.</t>
+          <t>Arterra Bioscience S.p.A.</t>
         </is>
       </c>
       <c r="B220" t="inlineStr">
@@ -12658,7 +12658,7 @@
     <row r="221">
       <c r="A221" t="inlineStr">
         <is>
-          <t>Com.Tel S.p.A.</t>
+          <t>Italian Wine Brands S.p.A.</t>
         </is>
       </c>
       <c r="B221" t="inlineStr">
@@ -12675,7 +12675,7 @@
     <row r="222">
       <c r="A222" t="inlineStr">
         <is>
-          <t>GAROFALO HEALTH CARE S.p.A.</t>
+          <t>ACQUAZZURRA S.p.A.</t>
         </is>
       </c>
       <c r="B222" t="inlineStr">
@@ -12692,7 +12692,7 @@
     <row r="223">
       <c r="A223" t="inlineStr">
         <is>
-          <t>GEL S.p.A.</t>
+          <t>ABC Company S.p.A. Società Benefit</t>
         </is>
       </c>
       <c r="B223" t="inlineStr">
@@ -12709,7 +12709,7 @@
     <row r="224">
       <c r="A224" t="inlineStr">
         <is>
-          <t>GREEN OLEO S.p.A</t>
+          <t>FRANCHETTI S.p.A.</t>
         </is>
       </c>
       <c r="B224" t="inlineStr">
@@ -12743,7 +12743,7 @@
     <row r="226">
       <c r="A226" t="inlineStr">
         <is>
-          <t>VALTECNE S.p.A.</t>
+          <t>Solid World Group S.p.A.</t>
         </is>
       </c>
       <c r="B226" t="inlineStr">
@@ -12760,7 +12760,7 @@
     <row r="227">
       <c r="A227" t="inlineStr">
         <is>
-          <t>Anima Holding S.p.A.</t>
+          <t>STMicroelectronics N.V.</t>
         </is>
       </c>
       <c r="B227" t="inlineStr">
@@ -12770,14 +12770,14 @@
       </c>
       <c r="C227" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="228">
       <c r="A228" t="inlineStr">
         <is>
-          <t>Dexelance S.p.A.</t>
+          <t>Nusco S.p.A.</t>
         </is>
       </c>
       <c r="B228" t="inlineStr">
@@ -12794,7 +12794,7 @@
     <row r="229">
       <c r="A229" t="inlineStr">
         <is>
-          <t>DigiTouch S.p.A.</t>
+          <t>EuroGroup Laminations S.p.A.</t>
         </is>
       </c>
       <c r="B229" t="inlineStr">
@@ -12811,7 +12811,7 @@
     <row r="230">
       <c r="A230" t="inlineStr">
         <is>
-          <t>EDILIZIACROBATICA S.p.A.</t>
+          <t>HIGH QUALITY FOOD S.p.A.</t>
         </is>
       </c>
       <c r="B230" t="inlineStr">
@@ -12821,14 +12821,14 @@
       </c>
       <c r="C230" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="231">
       <c r="A231" t="inlineStr">
         <is>
-          <t>Energy Time S.p.A.</t>
+          <t>IRCE s.p.a</t>
         </is>
       </c>
       <c r="B231" t="inlineStr">
@@ -12845,7 +12845,7 @@
     <row r="232">
       <c r="A232" t="inlineStr">
         <is>
-          <t>Unicredit S.p.A.</t>
+          <t>MARE ENGINEERING GROUP S.p.A.</t>
         </is>
       </c>
       <c r="B232" t="inlineStr">
@@ -12855,14 +12855,14 @@
       </c>
       <c r="C232" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="233">
       <c r="A233" t="inlineStr">
         <is>
-          <t>Nusco S.p.A.</t>
+          <t>Markbass S.p.A.</t>
         </is>
       </c>
       <c r="B233" t="inlineStr">
@@ -12872,14 +12872,14 @@
       </c>
       <c r="C233" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="234">
       <c r="A234" t="inlineStr">
         <is>
-          <t>Markbass S.p.A.</t>
+          <t>ACQUAZZURRA S.p.A.</t>
         </is>
       </c>
       <c r="B234" t="inlineStr">
@@ -12896,7 +12896,7 @@
     <row r="235">
       <c r="A235" t="inlineStr">
         <is>
-          <t>EuroGroup Laminations S.p.A.</t>
+          <t>Anima Holding S.p.A.</t>
         </is>
       </c>
       <c r="B235" t="inlineStr">
@@ -12906,14 +12906,14 @@
       </c>
       <c r="C235" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="236">
       <c r="A236" t="inlineStr">
         <is>
-          <t>Tecno S.p.A. Società Benefit</t>
+          <t>Dexelance S.p.A.</t>
         </is>
       </c>
       <c r="B236" t="inlineStr">
@@ -12923,14 +12923,14 @@
       </c>
       <c r="C236" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="237">
       <c r="A237" t="inlineStr">
         <is>
-          <t>Solid World Group S.p.A.</t>
+          <t>DigiTouch S.p.A.</t>
         </is>
       </c>
       <c r="B237" t="inlineStr">
@@ -12947,7 +12947,7 @@
     <row r="238">
       <c r="A238" t="inlineStr">
         <is>
-          <t>STMicroelectronics N.V.</t>
+          <t>Tecno S.p.A. Società Benefit</t>
         </is>
       </c>
       <c r="B238" t="inlineStr">
@@ -12957,14 +12957,14 @@
       </c>
       <c r="C238" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="239">
       <c r="A239" t="inlineStr">
         <is>
-          <t>ACQUAZZURRA S.p.A.</t>
+          <t>MARZOCCHI POMPE S.p.A.</t>
         </is>
       </c>
       <c r="B239" t="inlineStr">
@@ -12981,7 +12981,7 @@
     <row r="240">
       <c r="A240" t="inlineStr">
         <is>
-          <t>Valica S.p.A.</t>
+          <t>Energy Time S.p.A.</t>
         </is>
       </c>
       <c r="B240" t="inlineStr">
@@ -12998,7 +12998,7 @@
     <row r="241">
       <c r="A241" t="inlineStr">
         <is>
-          <t>MARZOCCHI POMPE S.p.A.</t>
+          <t>Unicredit S.p.A.</t>
         </is>
       </c>
       <c r="B241" t="inlineStr">
@@ -13008,14 +13008,14 @@
       </c>
       <c r="C241" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="242">
       <c r="A242" t="inlineStr">
         <is>
-          <t>MARE ENGINEERING GROUP S.p.A.</t>
+          <t>EDILIZIACROBATICA S.p.A.</t>
         </is>
       </c>
       <c r="B242" t="inlineStr">
@@ -13025,14 +13025,14 @@
       </c>
       <c r="C242" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="243">
       <c r="A243" t="inlineStr">
         <is>
-          <t>IRCE s.p.a</t>
+          <t>Valica S.p.A.</t>
         </is>
       </c>
       <c r="B243" t="inlineStr">
@@ -13049,7 +13049,7 @@
     <row r="244">
       <c r="A244" t="inlineStr">
         <is>
-          <t>HIGH QUALITY FOOD S.p.A.</t>
+          <t>VALTECNE S.p.A.</t>
         </is>
       </c>
       <c r="B244" t="inlineStr">
@@ -13083,7 +13083,7 @@
     <row r="246">
       <c r="A246" t="inlineStr">
         <is>
-          <t>Ferrari N.V.</t>
+          <t>TECHNOGYM S.p.A.</t>
         </is>
       </c>
       <c r="B246" t="inlineStr">
@@ -13093,14 +13093,14 @@
       </c>
       <c r="C246" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="247">
       <c r="A247" t="inlineStr">
         <is>
-          <t>Banco BPM S.p.A.</t>
+          <t>TECMA SOLUTIONS S.p.A.</t>
         </is>
       </c>
       <c r="B247" t="inlineStr">
@@ -13110,14 +13110,14 @@
       </c>
       <c r="C247" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="248">
       <c r="A248" t="inlineStr">
         <is>
-          <t>AMPLIFON S.p.A.</t>
+          <t>UCapital24 S.p.A.</t>
         </is>
       </c>
       <c r="B248" t="inlineStr">
@@ -13127,14 +13127,14 @@
       </c>
       <c r="C248" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="249">
       <c r="A249" t="inlineStr">
         <is>
-          <t>AMPLIFON S.p.A.</t>
+          <t>Unicredit S.p.A.</t>
         </is>
       </c>
       <c r="B249" t="inlineStr">
@@ -13151,7 +13151,7 @@
     <row r="250">
       <c r="A250" t="inlineStr">
         <is>
-          <t>Ariston Holding N.V.</t>
+          <t>Leonardo S.p.A.</t>
         </is>
       </c>
       <c r="B250" t="inlineStr">
@@ -13161,14 +13161,14 @@
       </c>
       <c r="C250" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="251">
       <c r="A251" t="inlineStr">
         <is>
-          <t>CREDITO EMILIANO S.p.A.</t>
+          <t>AMPLIFON S.p.A.</t>
         </is>
       </c>
       <c r="B251" t="inlineStr">
@@ -13178,14 +13178,14 @@
       </c>
       <c r="C251" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="252">
       <c r="A252" t="inlineStr">
         <is>
-          <t>Leonardo S.p.A.</t>
+          <t>AMPLIFON S.p.A.</t>
         </is>
       </c>
       <c r="B252" t="inlineStr">
@@ -13202,7 +13202,7 @@
     <row r="253">
       <c r="A253" t="inlineStr">
         <is>
-          <t>Kruso Kapital S.p.A.</t>
+          <t>Ariston Holding N.V.</t>
         </is>
       </c>
       <c r="B253" t="inlineStr">
@@ -13212,14 +13212,14 @@
       </c>
       <c r="C253" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="254">
       <c r="A254" t="inlineStr">
         <is>
-          <t>Laboratorio Farmaceutico Erfo S.p.A.</t>
+          <t>Banco BPM S.p.A.</t>
         </is>
       </c>
       <c r="B254" t="inlineStr">
@@ -13229,14 +13229,14 @@
       </c>
       <c r="C254" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="255">
       <c r="A255" t="inlineStr">
         <is>
-          <t>Unicredit S.p.A.</t>
+          <t>CREDITO EMILIANO S.p.A.</t>
         </is>
       </c>
       <c r="B255" t="inlineStr">
@@ -13246,14 +13246,14 @@
       </c>
       <c r="C255" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="256">
       <c r="A256" t="inlineStr">
         <is>
-          <t>UCapital24 S.p.A.</t>
+          <t>PLANETEL S.p.A.</t>
         </is>
       </c>
       <c r="B256" t="inlineStr">
@@ -13270,7 +13270,7 @@
     <row r="257">
       <c r="A257" t="inlineStr">
         <is>
-          <t>TECMA SOLUTIONS S.p.A.</t>
+          <t>Lucisano Media Group S.p.A.</t>
         </is>
       </c>
       <c r="B257" t="inlineStr">
@@ -13287,7 +13287,7 @@
     <row r="258">
       <c r="A258" t="inlineStr">
         <is>
-          <t>TECHNOGYM S.p.A.</t>
+          <t>ROSETTI MARINO S.p.A.</t>
         </is>
       </c>
       <c r="B258" t="inlineStr">
@@ -13304,7 +13304,7 @@
     <row r="259">
       <c r="A259" t="inlineStr">
         <is>
-          <t>ROSETTI MARINO S.p.A.</t>
+          <t>IMMSI S.p.A.</t>
         </is>
       </c>
       <c r="B259" t="inlineStr">
@@ -13321,7 +13321,7 @@
     <row r="260">
       <c r="A260" t="inlineStr">
         <is>
-          <t>PLANETEL S.p.A.</t>
+          <t>Laboratorio Farmaceutico Erfo S.p.A.</t>
         </is>
       </c>
       <c r="B260" t="inlineStr">
@@ -13338,7 +13338,7 @@
     <row r="261">
       <c r="A261" t="inlineStr">
         <is>
-          <t>Lucisano Media Group S.p.A.</t>
+          <t>Kruso Kapital S.p.A.</t>
         </is>
       </c>
       <c r="B261" t="inlineStr">
@@ -13348,14 +13348,14 @@
       </c>
       <c r="C261" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="262">
       <c r="A262" t="inlineStr">
         <is>
-          <t>Lottomatica Group S.p.A.</t>
+          <t>KALEON S.P.A.</t>
         </is>
       </c>
       <c r="B262" t="inlineStr">
@@ -13365,7 +13365,7 @@
       </c>
       <c r="C262" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
@@ -13389,7 +13389,7 @@
     <row r="264">
       <c r="A264" t="inlineStr">
         <is>
-          <t>First Capital S.p.A.</t>
+          <t>Italgas S.p.A.</t>
         </is>
       </c>
       <c r="B264" t="inlineStr">
@@ -13399,14 +13399,14 @@
       </c>
       <c r="C264" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="265">
       <c r="A265" t="inlineStr">
         <is>
-          <t>IMMSI S.p.A.</t>
+          <t>Intred S.p.A.</t>
         </is>
       </c>
       <c r="B265" t="inlineStr">
@@ -13416,14 +13416,14 @@
       </c>
       <c r="C265" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="266">
       <c r="A266" t="inlineStr">
         <is>
-          <t>Intred S.p.A.</t>
+          <t>Lottomatica Group S.p.A.</t>
         </is>
       </c>
       <c r="B266" t="inlineStr">
@@ -13440,7 +13440,7 @@
     <row r="267">
       <c r="A267" t="inlineStr">
         <is>
-          <t>Italgas S.p.A.</t>
+          <t>First Capital S.p.A.</t>
         </is>
       </c>
       <c r="B267" t="inlineStr">
@@ -13450,7 +13450,7 @@
       </c>
       <c r="C267" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
@@ -13467,14 +13467,14 @@
       </c>
       <c r="C268" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="269">
       <c r="A269" t="inlineStr">
         <is>
-          <t>KALEON S.P.A.</t>
+          <t>Ferrari N.V.</t>
         </is>
       </c>
       <c r="B269" t="inlineStr">
@@ -13484,14 +13484,14 @@
       </c>
       <c r="C269" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="270">
       <c r="A270" t="inlineStr">
         <is>
-          <t>Esprinet S.p.A.</t>
+          <t>EL.EN. S.p.A.</t>
         </is>
       </c>
       <c r="B270" t="inlineStr">
@@ -13501,14 +13501,14 @@
       </c>
       <c r="C270" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="271">
       <c r="A271" t="inlineStr">
         <is>
-          <t>FinecoBank S.p.A.</t>
+          <t>Banca Generali S.p.A.</t>
         </is>
       </c>
       <c r="B271" t="inlineStr">
@@ -13525,7 +13525,7 @@
     <row r="272">
       <c r="A272" t="inlineStr">
         <is>
-          <t>Industrie De Nora S.p.A.</t>
+          <t>Arterra Bioscience S.p.A.</t>
         </is>
       </c>
       <c r="B272" t="inlineStr">
@@ -13535,14 +13535,14 @@
       </c>
       <c r="C272" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="273">
       <c r="A273" t="inlineStr">
         <is>
-          <t>Industrie De Nora S.p.A.</t>
+          <t>ZIGNAGO VETRO S.p.A.</t>
         </is>
       </c>
       <c r="B273" t="inlineStr">
@@ -13552,14 +13552,14 @@
       </c>
       <c r="C273" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="274">
       <c r="A274" t="inlineStr">
         <is>
-          <t>Nexi S.p.A.</t>
+          <t>Bper Banca S.P.A.</t>
         </is>
       </c>
       <c r="B274" t="inlineStr">
@@ -13576,7 +13576,7 @@
     <row r="275">
       <c r="A275" t="inlineStr">
         <is>
-          <t>Poste Italiane S.p.A.</t>
+          <t>CELLULARLINE S.p.A.</t>
         </is>
       </c>
       <c r="B275" t="inlineStr">
@@ -13593,7 +13593,7 @@
     <row r="276">
       <c r="A276" t="inlineStr">
         <is>
-          <t>TECHNOGYM S.p.A.</t>
+          <t>CELLULARLINE S.p.A.</t>
         </is>
       </c>
       <c r="B276" t="inlineStr">
@@ -13603,14 +13603,14 @@
       </c>
       <c r="C276" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="277">
       <c r="A277" t="inlineStr">
         <is>
-          <t>TECHNOGYM S.p.A.</t>
+          <t>Davide Campari-Milano N.V.</t>
         </is>
       </c>
       <c r="B277" t="inlineStr">
@@ -13620,14 +13620,14 @@
       </c>
       <c r="C277" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="278">
       <c r="A278" t="inlineStr">
         <is>
-          <t>TELECOM ITALIA S.p.A.</t>
+          <t>Davide Campari-Milano N.V.</t>
         </is>
       </c>
       <c r="B278" t="inlineStr">
@@ -13637,14 +13637,14 @@
       </c>
       <c r="C278" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="279">
       <c r="A279" t="inlineStr">
         <is>
-          <t>Lottomatica Group S.p.A.</t>
+          <t>Eni S.p.A.</t>
         </is>
       </c>
       <c r="B279" t="inlineStr">
@@ -13654,14 +13654,14 @@
       </c>
       <c r="C279" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="280">
       <c r="A280" t="inlineStr">
         <is>
-          <t>Arterra Bioscience S.p.A.</t>
+          <t>EDISON S.p.A.</t>
         </is>
       </c>
       <c r="B280" t="inlineStr">
@@ -13678,7 +13678,7 @@
     <row r="281">
       <c r="A281" t="inlineStr">
         <is>
-          <t>CELLULARLINE S.p.A.</t>
+          <t>TRAWELL CO S.p.A.</t>
         </is>
       </c>
       <c r="B281" t="inlineStr">
@@ -13688,14 +13688,14 @@
       </c>
       <c r="C281" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Bod Annual Report</t>
         </is>
       </c>
     </row>
     <row r="282">
       <c r="A282" t="inlineStr">
         <is>
-          <t>Bper Banca S.P.A.</t>
+          <t>TECHNOGYM S.p.A.</t>
         </is>
       </c>
       <c r="B282" t="inlineStr">
@@ -13712,7 +13712,7 @@
     <row r="283">
       <c r="A283" t="inlineStr">
         <is>
-          <t>CELLULARLINE S.p.A.</t>
+          <t>TECHNOGYM S.p.A.</t>
         </is>
       </c>
       <c r="B283" t="inlineStr">
@@ -13729,7 +13729,7 @@
     <row r="284">
       <c r="A284" t="inlineStr">
         <is>
-          <t>Davide Campari-Milano N.V.</t>
+          <t>Poste Italiane S.p.A.</t>
         </is>
       </c>
       <c r="B284" t="inlineStr">
@@ -13746,7 +13746,7 @@
     <row r="285">
       <c r="A285" t="inlineStr">
         <is>
-          <t>Davide Campari-Milano N.V.</t>
+          <t>Nexi S.p.A.</t>
         </is>
       </c>
       <c r="B285" t="inlineStr">
@@ -13756,14 +13756,14 @@
       </c>
       <c r="C285" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="286">
       <c r="A286" t="inlineStr">
         <is>
-          <t>EDISON S.p.A.</t>
+          <t>Lottomatica Group S.p.A.</t>
         </is>
       </c>
       <c r="B286" t="inlineStr">
@@ -13773,14 +13773,14 @@
       </c>
       <c r="C286" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="287">
       <c r="A287" t="inlineStr">
         <is>
-          <t>EL.EN. S.p.A.</t>
+          <t>Industrie De Nora S.p.A.</t>
         </is>
       </c>
       <c r="B287" t="inlineStr">
@@ -13790,14 +13790,14 @@
       </c>
       <c r="C287" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="288">
       <c r="A288" t="inlineStr">
         <is>
-          <t>Ariston Holding N.V.</t>
+          <t>Industrie De Nora S.p.A.</t>
         </is>
       </c>
       <c r="B288" t="inlineStr">
@@ -13807,14 +13807,14 @@
       </c>
       <c r="C288" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="289">
       <c r="A289" t="inlineStr">
         <is>
-          <t>Ariston Holding N.V.</t>
+          <t>FinecoBank S.p.A.</t>
         </is>
       </c>
       <c r="B289" t="inlineStr">
@@ -13824,14 +13824,14 @@
       </c>
       <c r="C289" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="290">
       <c r="A290" t="inlineStr">
         <is>
-          <t>ZIGNAGO VETRO S.p.A.</t>
+          <t>TELECOM ITALIA S.p.A.</t>
         </is>
       </c>
       <c r="B290" t="inlineStr">
@@ -13841,14 +13841,14 @@
       </c>
       <c r="C290" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="291">
       <c r="A291" t="inlineStr">
         <is>
-          <t>ZIGNAGO VETRO S.p.A.</t>
+          <t>Esprinet S.p.A.</t>
         </is>
       </c>
       <c r="B291" t="inlineStr">
@@ -13858,14 +13858,14 @@
       </c>
       <c r="C291" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="292">
       <c r="A292" t="inlineStr">
         <is>
-          <t>TRAWELL CO S.p.A.</t>
+          <t>Ariston Holding N.V.</t>
         </is>
       </c>
       <c r="B292" t="inlineStr">
@@ -13875,14 +13875,14 @@
       </c>
       <c r="C292" t="inlineStr">
         <is>
-          <t>Bod Annual Report</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="293">
       <c r="A293" t="inlineStr">
         <is>
-          <t>Banca Generali S.p.A.</t>
+          <t>Ariston Holding N.V.</t>
         </is>
       </c>
       <c r="B293" t="inlineStr">
@@ -13892,14 +13892,14 @@
       </c>
       <c r="C293" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="294">
       <c r="A294" t="inlineStr">
         <is>
-          <t>Eni S.p.A.</t>
+          <t>ZIGNAGO VETRO S.p.A.</t>
         </is>
       </c>
       <c r="B294" t="inlineStr">
@@ -13909,14 +13909,14 @@
       </c>
       <c r="C294" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="295">
       <c r="A295" t="inlineStr">
         <is>
-          <t>SAFILO GROUP S.p.A.</t>
+          <t>TERNA S.p.A.</t>
         </is>
       </c>
       <c r="B295" t="inlineStr">
@@ -13926,7 +13926,7 @@
       </c>
       <c r="C295" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
@@ -13950,7 +13950,7 @@
     <row r="297">
       <c r="A297" t="inlineStr">
         <is>
-          <t>TERNA S.p.A.</t>
+          <t>FinecoBank S.p.A.</t>
         </is>
       </c>
       <c r="B297" t="inlineStr">
@@ -13967,7 +13967,7 @@
     <row r="298">
       <c r="A298" t="inlineStr">
         <is>
-          <t>TERNA S.p.A.</t>
+          <t>Generalfinance S.p.A.</t>
         </is>
       </c>
       <c r="B298" t="inlineStr">
@@ -13984,7 +13984,7 @@
     <row r="299">
       <c r="A299" t="inlineStr">
         <is>
-          <t>TELECOM ITALIA S.p.A.</t>
+          <t>ENEL S.p.A.</t>
         </is>
       </c>
       <c r="B299" t="inlineStr">
@@ -14001,7 +14001,7 @@
     <row r="300">
       <c r="A300" t="inlineStr">
         <is>
-          <t>RCS MediaGroup S.p.A.</t>
+          <t>TELECOM ITALIA S.p.A.</t>
         </is>
       </c>
       <c r="B300" t="inlineStr">
@@ -14011,14 +14011,14 @@
       </c>
       <c r="C300" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="301">
       <c r="A301" t="inlineStr">
         <is>
-          <t>SIT S.p.A.</t>
+          <t>TERNA S.p.A.</t>
         </is>
       </c>
       <c r="B301" t="inlineStr">
@@ -14052,7 +14052,7 @@
     <row r="303">
       <c r="A303" t="inlineStr">
         <is>
-          <t>Generalfinance S.p.A.</t>
+          <t>IGD SIIQ S.p.A.</t>
         </is>
       </c>
       <c r="B303" t="inlineStr">
@@ -14069,7 +14069,7 @@
     <row r="304">
       <c r="A304" t="inlineStr">
         <is>
-          <t>Pirelli &amp; C. S.p.A.</t>
+          <t>SAFILO GROUP S.p.A.</t>
         </is>
       </c>
       <c r="B304" t="inlineStr">
@@ -14086,7 +14086,7 @@
     <row r="305">
       <c r="A305" t="inlineStr">
         <is>
-          <t>FinecoBank S.p.A.</t>
+          <t>ENEL S.p.A.</t>
         </is>
       </c>
       <c r="B305" t="inlineStr">
@@ -14096,14 +14096,14 @@
       </c>
       <c r="C305" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="306">
       <c r="A306" t="inlineStr">
         <is>
-          <t>FRENDY ENERGY S.p.A.</t>
+          <t>RCS MediaGroup S.p.A.</t>
         </is>
       </c>
       <c r="B306" t="inlineStr">
@@ -14120,7 +14120,7 @@
     <row r="307">
       <c r="A307" t="inlineStr">
         <is>
-          <t>FINE FOODS &amp; Pharmaceuticals N.T.M. S.p.A.</t>
+          <t>BANCO DI DESIO E DELLA BRIANZA S.p.A.</t>
         </is>
       </c>
       <c r="B307" t="inlineStr">
@@ -14137,7 +14137,7 @@
     <row r="308">
       <c r="A308" t="inlineStr">
         <is>
-          <t>EUROCOMMERCIAL PROPERTIES N.V.</t>
+          <t>BANCA MEDIOLANUM S.p.A.</t>
         </is>
       </c>
       <c r="B308" t="inlineStr">
@@ -14154,7 +14154,7 @@
     <row r="309">
       <c r="A309" t="inlineStr">
         <is>
-          <t>ENEL S.p.A.</t>
+          <t>BANCA IFIS S.p.A.</t>
         </is>
       </c>
       <c r="B309" t="inlineStr">
@@ -14171,7 +14171,7 @@
     <row r="310">
       <c r="A310" t="inlineStr">
         <is>
-          <t>ENEL S.p.A.</t>
+          <t>BANCA IFIS S.p.A.</t>
         </is>
       </c>
       <c r="B310" t="inlineStr">
@@ -14188,7 +14188,7 @@
     <row r="311">
       <c r="A311" t="inlineStr">
         <is>
-          <t>Directa SIM S.P.A.</t>
+          <t>AZIMUT HOLDING S.p.A.</t>
         </is>
       </c>
       <c r="B311" t="inlineStr">
@@ -14198,14 +14198,14 @@
       </c>
       <c r="C311" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="312">
       <c r="A312" t="inlineStr">
         <is>
-          <t>D'AMICO INTERNATIONAL SHIPPING S.A.</t>
+          <t>ASCOPIAVE S.p.A.</t>
         </is>
       </c>
       <c r="B312" t="inlineStr">
@@ -14222,7 +14222,7 @@
     <row r="313">
       <c r="A313" t="inlineStr">
         <is>
-          <t>D'AMICO INTERNATIONAL SHIPPING S.A.</t>
+          <t>ASCOPIAVE S.p.A.</t>
         </is>
       </c>
       <c r="B313" t="inlineStr">
@@ -14239,7 +14239,7 @@
     <row r="314">
       <c r="A314" t="inlineStr">
         <is>
-          <t>Banca Monte dei Paschi di Siena S.p.A.</t>
+          <t>FRENDY ENERGY S.p.A.</t>
         </is>
       </c>
       <c r="B314" t="inlineStr">
@@ -14249,14 +14249,14 @@
       </c>
       <c r="C314" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="315">
       <c r="A315" t="inlineStr">
         <is>
-          <t>Banca Profilo S.p.A.</t>
+          <t>SIT S.p.A.</t>
         </is>
       </c>
       <c r="B315" t="inlineStr">
@@ -14273,7 +14273,7 @@
     <row r="316">
       <c r="A316" t="inlineStr">
         <is>
-          <t>Bper Banca S.P.A.</t>
+          <t>Directa SIM S.P.A.</t>
         </is>
       </c>
       <c r="B316" t="inlineStr">
@@ -14283,14 +14283,14 @@
       </c>
       <c r="C316" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="317">
       <c r="A317" t="inlineStr">
         <is>
-          <t>CAIRO COMMUNICATION S.p.A.</t>
+          <t>BREMBO N.V.</t>
         </is>
       </c>
       <c r="B317" t="inlineStr">
@@ -14300,14 +14300,14 @@
       </c>
       <c r="C317" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="318">
       <c r="A318" t="inlineStr">
         <is>
-          <t>CALTAGIRONE S.p.A.</t>
+          <t>D'AMICO INTERNATIONAL SHIPPING S.A.</t>
         </is>
       </c>
       <c r="B318" t="inlineStr">
@@ -14317,14 +14317,14 @@
       </c>
       <c r="C318" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="319">
       <c r="A319" t="inlineStr">
         <is>
-          <t>COMPAGNIA DEI CARAIBI S.p.A.</t>
+          <t>INTERCOS S.p.A.</t>
         </is>
       </c>
       <c r="B319" t="inlineStr">
@@ -14334,14 +14334,14 @@
       </c>
       <c r="C319" t="inlineStr">
         <is>
-          <t>Bod Annual Report</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="320">
       <c r="A320" t="inlineStr">
         <is>
-          <t>Cementir Holding N.V.</t>
+          <t>INTERCOS S.p.A.</t>
         </is>
       </c>
       <c r="B320" t="inlineStr">
@@ -14358,7 +14358,7 @@
     <row r="321">
       <c r="A321" t="inlineStr">
         <is>
-          <t>CleanBnB S.p.A.</t>
+          <t>Iveco Group N.V.</t>
         </is>
       </c>
       <c r="B321" t="inlineStr">
@@ -14368,14 +14368,14 @@
       </c>
       <c r="C321" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="322">
       <c r="A322" t="inlineStr">
         <is>
-          <t>BANCA IFIS S.p.A.</t>
+          <t>Leonardo S.p.A.</t>
         </is>
       </c>
       <c r="B322" t="inlineStr">
@@ -14385,14 +14385,14 @@
       </c>
       <c r="C322" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="323">
       <c r="A323" t="inlineStr">
         <is>
-          <t>BANCA IFIS S.p.A.</t>
+          <t>Mediobanca Banca di Credito Finanziario S.p.A.</t>
         </is>
       </c>
       <c r="B323" t="inlineStr">
@@ -14402,14 +14402,14 @@
       </c>
       <c r="C323" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="324">
       <c r="A324" t="inlineStr">
         <is>
-          <t>BANCA MEDIOLANUM S.p.A.</t>
+          <t>Nexi S.p.A.</t>
         </is>
       </c>
       <c r="B324" t="inlineStr">
@@ -14419,14 +14419,14 @@
       </c>
       <c r="C324" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="325">
       <c r="A325" t="inlineStr">
         <is>
-          <t>BANCO DI DESIO E DELLA BRIANZA S.p.A.</t>
+          <t>Pirelli &amp; C. S.p.A.</t>
         </is>
       </c>
       <c r="B325" t="inlineStr">
@@ -14443,7 +14443,7 @@
     <row r="326">
       <c r="A326" t="inlineStr">
         <is>
-          <t>Comer Industries S.p.A.</t>
+          <t>Poste Italiane S.p.A.</t>
         </is>
       </c>
       <c r="B326" t="inlineStr">
@@ -14453,14 +14453,14 @@
       </c>
       <c r="C326" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="327">
       <c r="A327" t="inlineStr">
         <is>
-          <t>Poste Italiane S.p.A.</t>
+          <t>EUROCOMMERCIAL PROPERTIES N.V.</t>
         </is>
       </c>
       <c r="B327" t="inlineStr">
@@ -14470,14 +14470,14 @@
       </c>
       <c r="C327" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="328">
       <c r="A328" t="inlineStr">
         <is>
-          <t>AZIMUT HOLDING S.p.A.</t>
+          <t>Comer Industries S.p.A.</t>
         </is>
       </c>
       <c r="B328" t="inlineStr">
@@ -14494,7 +14494,7 @@
     <row r="329">
       <c r="A329" t="inlineStr">
         <is>
-          <t>ASCOPIAVE S.p.A.</t>
+          <t>CleanBnB S.p.A.</t>
         </is>
       </c>
       <c r="B329" t="inlineStr">
@@ -14504,14 +14504,14 @@
       </c>
       <c r="C329" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="330">
       <c r="A330" t="inlineStr">
         <is>
-          <t>ASCOPIAVE S.p.A.</t>
+          <t>Cementir Holding N.V.</t>
         </is>
       </c>
       <c r="B330" t="inlineStr">
@@ -14528,7 +14528,7 @@
     <row r="331">
       <c r="A331" t="inlineStr">
         <is>
-          <t>BREMBO N.V.</t>
+          <t>COMPAGNIA DEI CARAIBI S.p.A.</t>
         </is>
       </c>
       <c r="B331" t="inlineStr">
@@ -14538,14 +14538,14 @@
       </c>
       <c r="C331" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Bod Annual Report</t>
         </is>
       </c>
     </row>
     <row r="332">
       <c r="A332" t="inlineStr">
         <is>
-          <t>Nexi S.p.A.</t>
+          <t>CALTAGIRONE S.p.A.</t>
         </is>
       </c>
       <c r="B332" t="inlineStr">
@@ -14555,14 +14555,14 @@
       </c>
       <c r="C332" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="333">
       <c r="A333" t="inlineStr">
         <is>
-          <t>Mediobanca Banca di Credito Finanziario S.p.A.</t>
+          <t>CAIRO COMMUNICATION S.p.A.</t>
         </is>
       </c>
       <c r="B333" t="inlineStr">
@@ -14572,14 +14572,14 @@
       </c>
       <c r="C333" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="334">
       <c r="A334" t="inlineStr">
         <is>
-          <t>Leonardo S.p.A.</t>
+          <t>Bper Banca S.P.A.</t>
         </is>
       </c>
       <c r="B334" t="inlineStr">
@@ -14589,14 +14589,14 @@
       </c>
       <c r="C334" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="335">
       <c r="A335" t="inlineStr">
         <is>
-          <t>Iveco Group N.V.</t>
+          <t>Banca Profilo S.p.A.</t>
         </is>
       </c>
       <c r="B335" t="inlineStr">
@@ -14613,7 +14613,7 @@
     <row r="336">
       <c r="A336" t="inlineStr">
         <is>
-          <t>INTERCOS S.p.A.</t>
+          <t>Banca Monte dei Paschi di Siena S.p.A.</t>
         </is>
       </c>
       <c r="B336" t="inlineStr">
@@ -14630,7 +14630,7 @@
     <row r="337">
       <c r="A337" t="inlineStr">
         <is>
-          <t>INTERCOS S.p.A.</t>
+          <t>Growens S.p.A.</t>
         </is>
       </c>
       <c r="B337" t="inlineStr">
@@ -14640,14 +14640,14 @@
       </c>
       <c r="C337" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="338">
       <c r="A338" t="inlineStr">
         <is>
-          <t>IGD SIIQ S.p.A.</t>
+          <t>D'AMICO INTERNATIONAL SHIPPING S.A.</t>
         </is>
       </c>
       <c r="B338" t="inlineStr">
@@ -14664,7 +14664,7 @@
     <row r="339">
       <c r="A339" t="inlineStr">
         <is>
-          <t>Growens S.p.A.</t>
+          <t>FINE FOODS &amp; Pharmaceuticals N.T.M. S.p.A.</t>
         </is>
       </c>
       <c r="B339" t="inlineStr">
@@ -14715,7 +14715,7 @@
     <row r="342">
       <c r="A342" t="inlineStr">
         <is>
-          <t>Intesa Sanpaolo S.p.A.</t>
+          <t>TESMEC S.p.A.</t>
         </is>
       </c>
       <c r="B342" t="inlineStr">
@@ -14732,7 +14732,7 @@
     <row r="343">
       <c r="A343" t="inlineStr">
         <is>
-          <t>PIAGGIO &amp; C. S.p.A.</t>
+          <t>Sanlorenzo S.p.A.</t>
         </is>
       </c>
       <c r="B343" t="inlineStr">
@@ -14742,14 +14742,14 @@
       </c>
       <c r="C343" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="344">
       <c r="A344" t="inlineStr">
         <is>
-          <t>Riba Mundo Tecnologia S.A.</t>
+          <t>Simone S.p.A.</t>
         </is>
       </c>
       <c r="B344" t="inlineStr">
@@ -14759,14 +14759,14 @@
       </c>
       <c r="C344" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Bod Annual Report</t>
         </is>
       </c>
     </row>
     <row r="345">
       <c r="A345" t="inlineStr">
         <is>
-          <t>Sanlorenzo S.p.A.</t>
+          <t>TESMEC S.p.A.</t>
         </is>
       </c>
       <c r="B345" t="inlineStr">
@@ -14783,7 +14783,7 @@
     <row r="346">
       <c r="A346" t="inlineStr">
         <is>
-          <t>Simone S.p.A.</t>
+          <t>PIAGGIO &amp; C. S.p.A.</t>
         </is>
       </c>
       <c r="B346" t="inlineStr">
@@ -14793,14 +14793,14 @@
       </c>
       <c r="C346" t="inlineStr">
         <is>
-          <t>Bod Annual Report</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="347">
       <c r="A347" t="inlineStr">
         <is>
-          <t>TESMEC S.p.A.</t>
+          <t>Litix S.p.A.</t>
         </is>
       </c>
       <c r="B347" t="inlineStr">
@@ -14810,14 +14810,14 @@
       </c>
       <c r="C347" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="348">
       <c r="A348" t="inlineStr">
         <is>
-          <t>TESMEC S.p.A.</t>
+          <t>Intesa Sanpaolo S.p.A.</t>
         </is>
       </c>
       <c r="B348" t="inlineStr">
@@ -14827,14 +14827,14 @@
       </c>
       <c r="C348" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="349">
       <c r="A349" t="inlineStr">
         <is>
-          <t>Litix S.p.A.</t>
+          <t>Intesa Sanpaolo S.p.A.</t>
         </is>
       </c>
       <c r="B349" t="inlineStr">
@@ -14844,14 +14844,14 @@
       </c>
       <c r="C349" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="350">
       <c r="A350" t="inlineStr">
         <is>
-          <t>Intesa Sanpaolo S.p.A.</t>
+          <t>PIAGGIO &amp; C. S.p.A.</t>
         </is>
       </c>
       <c r="B350" t="inlineStr">
@@ -14868,7 +14868,7 @@
     <row r="351">
       <c r="A351" t="inlineStr">
         <is>
-          <t>PIAGGIO &amp; C. S.p.A.</t>
+          <t>Riba Mundo Tecnologia S.A.</t>
         </is>
       </c>
       <c r="B351" t="inlineStr">
@@ -14885,7 +14885,7 @@
     <row r="352">
       <c r="A352" t="inlineStr">
         <is>
-          <t>BEEWIZE</t>
+          <t>VALSOIA S.p.A.</t>
         </is>
       </c>
       <c r="B352" t="inlineStr">
@@ -14902,7 +14902,7 @@
     <row r="353">
       <c r="A353" t="inlineStr">
         <is>
-          <t>IREN S.p.A.</t>
+          <t>UNIDATA S.p.A.</t>
         </is>
       </c>
       <c r="B353" t="inlineStr">
@@ -14912,14 +14912,14 @@
       </c>
       <c r="C353" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="354">
       <c r="A354" t="inlineStr">
         <is>
-          <t>Farmacosmo S.p.A.</t>
+          <t>Svas Biosana S.p.A.</t>
         </is>
       </c>
       <c r="B354" t="inlineStr">
@@ -14936,7 +14936,7 @@
     <row r="355">
       <c r="A355" t="inlineStr">
         <is>
-          <t>VALSOIA S.p.A.</t>
+          <t>SECO S.p.A.</t>
         </is>
       </c>
       <c r="B355" t="inlineStr">
@@ -14953,7 +14953,7 @@
     <row r="356">
       <c r="A356" t="inlineStr">
         <is>
-          <t>UNIDATA S.p.A.</t>
+          <t>Pharmanutra S.p.A.</t>
         </is>
       </c>
       <c r="B356" t="inlineStr">
@@ -14963,14 +14963,14 @@
       </c>
       <c r="C356" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="357">
       <c r="A357" t="inlineStr">
         <is>
-          <t>Svas Biosana S.p.A.</t>
+          <t>IREN S.p.A.</t>
         </is>
       </c>
       <c r="B357" t="inlineStr">
@@ -14987,7 +14987,7 @@
     <row r="358">
       <c r="A358" t="inlineStr">
         <is>
-          <t>SECO S.p.A.</t>
+          <t>Farmacosmo S.p.A.</t>
         </is>
       </c>
       <c r="B358" t="inlineStr">
@@ -15004,7 +15004,7 @@
     <row r="359">
       <c r="A359" t="inlineStr">
         <is>
-          <t>Pharmanutra S.p.A.</t>
+          <t>FINCANTIERI S.p.A.</t>
         </is>
       </c>
       <c r="B359" t="inlineStr">
@@ -15021,7 +15021,7 @@
     <row r="360">
       <c r="A360" t="inlineStr">
         <is>
-          <t>BFF Bank S.P.A.</t>
+          <t>BEEWIZE</t>
         </is>
       </c>
       <c r="B360" t="inlineStr">
@@ -15038,7 +15038,7 @@
     <row r="361">
       <c r="A361" t="inlineStr">
         <is>
-          <t>FINCANTIERI S.p.A.</t>
+          <t>BFF Bank S.P.A.</t>
         </is>
       </c>
       <c r="B361" t="inlineStr">
@@ -15055,7 +15055,7 @@
     <row r="362">
       <c r="A362" t="inlineStr">
         <is>
-          <t>Gismondi 1754 S.p.A.</t>
+          <t>CALEFFI S.p.A.</t>
         </is>
       </c>
       <c r="B362" t="inlineStr">
@@ -15072,7 +15072,7 @@
     <row r="363">
       <c r="A363" t="inlineStr">
         <is>
-          <t>Enervit S.p.A.</t>
+          <t>DE' LONGHI S.p.A.</t>
         </is>
       </c>
       <c r="B363" t="inlineStr">
@@ -15082,14 +15082,14 @@
       </c>
       <c r="C363" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="364">
       <c r="A364" t="inlineStr">
         <is>
-          <t>INWIT S.p.A.</t>
+          <t>RECORDATI S.p.A.</t>
         </is>
       </c>
       <c r="B364" t="inlineStr">
@@ -15106,7 +15106,7 @@
     <row r="365">
       <c r="A365" t="inlineStr">
         <is>
-          <t>Indel B S.p.A.</t>
+          <t>SAIPEM S.p.A.</t>
         </is>
       </c>
       <c r="B365" t="inlineStr">
@@ -15116,14 +15116,14 @@
       </c>
       <c r="C365" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="366">
       <c r="A366" t="inlineStr">
         <is>
-          <t>LU-VE S.p.A.</t>
+          <t>SOL S.p.A.</t>
         </is>
       </c>
       <c r="B366" t="inlineStr">
@@ -15133,14 +15133,14 @@
       </c>
       <c r="C366" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="367">
       <c r="A367" t="inlineStr">
         <is>
-          <t>LU-VE S.p.A.</t>
+          <t>SOL S.p.A.</t>
         </is>
       </c>
       <c r="B367" t="inlineStr">
@@ -15157,7 +15157,7 @@
     <row r="368">
       <c r="A368" t="inlineStr">
         <is>
-          <t>ENEL S.p.A.</t>
+          <t>TENARIS S.A.</t>
         </is>
       </c>
       <c r="B368" t="inlineStr">
@@ -15174,7 +15174,7 @@
     <row r="369">
       <c r="A369" t="inlineStr">
         <is>
-          <t>EMAK S.p.A.</t>
+          <t>TERNA S.p.A.</t>
         </is>
       </c>
       <c r="B369" t="inlineStr">
@@ -15184,14 +15184,14 @@
       </c>
       <c r="C369" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="370">
       <c r="A370" t="inlineStr">
         <is>
-          <t>ENAV S.p.A.</t>
+          <t>UNIDATA S.p.A.</t>
         </is>
       </c>
       <c r="B370" t="inlineStr">
@@ -15208,7 +15208,7 @@
     <row r="371">
       <c r="A371" t="inlineStr">
         <is>
-          <t>Digital Value S.p.A.</t>
+          <t>BANCA SISTEMA S.p.A.</t>
         </is>
       </c>
       <c r="B371" t="inlineStr">
@@ -15218,14 +15218,14 @@
       </c>
       <c r="C371" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="372">
       <c r="A372" t="inlineStr">
         <is>
-          <t>Dexelance S.p.A.</t>
+          <t>Avio S.p.A.</t>
         </is>
       </c>
       <c r="B372" t="inlineStr">
@@ -15235,14 +15235,14 @@
       </c>
       <c r="C372" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="373">
       <c r="A373" t="inlineStr">
         <is>
-          <t>DE' LONGHI S.p.A.</t>
+          <t>Confinvest Oro S.p.A.</t>
         </is>
       </c>
       <c r="B373" t="inlineStr">
@@ -15252,14 +15252,14 @@
       </c>
       <c r="C373" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="374">
       <c r="A374" t="inlineStr">
         <is>
-          <t>DE' LONGHI S.p.A.</t>
+          <t>BANCA SISTEMA S.p.A.</t>
         </is>
       </c>
       <c r="B374" t="inlineStr">
@@ -15269,14 +15269,14 @@
       </c>
       <c r="C374" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="375">
       <c r="A375" t="inlineStr">
         <is>
-          <t>CALEFFI S.p.A.</t>
+          <t>Dexelance S.p.A.</t>
         </is>
       </c>
       <c r="B375" t="inlineStr">
@@ -15286,14 +15286,14 @@
       </c>
       <c r="C375" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="376">
       <c r="A376" t="inlineStr">
         <is>
-          <t>BANCA SISTEMA S.p.A.</t>
+          <t>DE' LONGHI S.p.A.</t>
         </is>
       </c>
       <c r="B376" t="inlineStr">
@@ -15310,7 +15310,7 @@
     <row r="377">
       <c r="A377" t="inlineStr">
         <is>
-          <t>Avio S.p.A.</t>
+          <t>EMAK S.p.A.</t>
         </is>
       </c>
       <c r="B377" t="inlineStr">
@@ -15327,7 +15327,7 @@
     <row r="378">
       <c r="A378" t="inlineStr">
         <is>
-          <t>Confinvest Oro S.p.A.</t>
+          <t>PININFARINA S.p.A.</t>
         </is>
       </c>
       <c r="B378" t="inlineStr">
@@ -15337,7 +15337,7 @@
       </c>
       <c r="C378" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
@@ -15361,7 +15361,7 @@
     <row r="380">
       <c r="A380" t="inlineStr">
         <is>
-          <t>BANCA SISTEMA S.p.A.</t>
+          <t>VALTECNE S.p.A.</t>
         </is>
       </c>
       <c r="B380" t="inlineStr">
@@ -15371,14 +15371,14 @@
       </c>
       <c r="C380" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="381">
       <c r="A381" t="inlineStr">
         <is>
-          <t>PININFARINA S.p.A.</t>
+          <t>LU-VE S.p.A.</t>
         </is>
       </c>
       <c r="B381" t="inlineStr">
@@ -15395,7 +15395,7 @@
     <row r="382">
       <c r="A382" t="inlineStr">
         <is>
-          <t>TENARIS S.A.</t>
+          <t>LU-VE S.p.A.</t>
         </is>
       </c>
       <c r="B382" t="inlineStr">
@@ -15405,14 +15405,14 @@
       </c>
       <c r="C382" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="383">
       <c r="A383" t="inlineStr">
         <is>
-          <t>RECORDATI S.p.A.</t>
+          <t>Indel B S.p.A.</t>
         </is>
       </c>
       <c r="B383" t="inlineStr">
@@ -15429,7 +15429,7 @@
     <row r="384">
       <c r="A384" t="inlineStr">
         <is>
-          <t>SAIPEM S.p.A.</t>
+          <t>INWIT S.p.A.</t>
         </is>
       </c>
       <c r="B384" t="inlineStr">
@@ -15439,14 +15439,14 @@
       </c>
       <c r="C384" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="385">
       <c r="A385" t="inlineStr">
         <is>
-          <t>VALTECNE S.p.A.</t>
+          <t>Gismondi 1754 S.p.A.</t>
         </is>
       </c>
       <c r="B385" t="inlineStr">
@@ -15456,14 +15456,14 @@
       </c>
       <c r="C385" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="386">
       <c r="A386" t="inlineStr">
         <is>
-          <t>UNIDATA S.p.A.</t>
+          <t>Enervit S.p.A.</t>
         </is>
       </c>
       <c r="B386" t="inlineStr">
@@ -15480,7 +15480,7 @@
     <row r="387">
       <c r="A387" t="inlineStr">
         <is>
-          <t>TERNA S.p.A.</t>
+          <t>ENEL S.p.A.</t>
         </is>
       </c>
       <c r="B387" t="inlineStr">
@@ -15497,7 +15497,7 @@
     <row r="388">
       <c r="A388" t="inlineStr">
         <is>
-          <t>SOL S.p.A.</t>
+          <t>ENAV S.p.A.</t>
         </is>
       </c>
       <c r="B388" t="inlineStr">
@@ -15507,14 +15507,14 @@
       </c>
       <c r="C388" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="389">
       <c r="A389" t="inlineStr">
         <is>
-          <t>SOL S.p.A.</t>
+          <t>Digital Value S.p.A.</t>
         </is>
       </c>
       <c r="B389" t="inlineStr">
@@ -15524,14 +15524,14 @@
       </c>
       <c r="C389" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="390">
       <c r="A390" t="inlineStr">
         <is>
-          <t>NEWPRINCES</t>
+          <t>Fiera Milano S.p.A</t>
         </is>
       </c>
       <c r="B390" t="inlineStr">
@@ -15548,7 +15548,7 @@
     <row r="391">
       <c r="A391" t="inlineStr">
         <is>
-          <t>ARNOLDO MONDADORI EDITORE S.p.A.</t>
+          <t>RECORDATI S.p.A.</t>
         </is>
       </c>
       <c r="B391" t="inlineStr">
@@ -15565,7 +15565,7 @@
     <row r="392">
       <c r="A392" t="inlineStr">
         <is>
-          <t>POLIGRAFICI PRINTING S.p.A.</t>
+          <t>WIIT S.p.A.</t>
         </is>
       </c>
       <c r="B392" t="inlineStr">
@@ -15582,7 +15582,7 @@
     <row r="393">
       <c r="A393" t="inlineStr">
         <is>
-          <t>Pattern S.p.A.</t>
+          <t>ZEST S.p.A.</t>
         </is>
       </c>
       <c r="B393" t="inlineStr">
@@ -15599,7 +15599,7 @@
     <row r="394">
       <c r="A394" t="inlineStr">
         <is>
-          <t>RAI WAY S.p.A.</t>
+          <t>GEOX S.p.A.</t>
         </is>
       </c>
       <c r="B394" t="inlineStr">
@@ -15609,14 +15609,14 @@
       </c>
       <c r="C394" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="395">
       <c r="A395" t="inlineStr">
         <is>
-          <t>RCS MediaGroup S.p.A.</t>
+          <t>WIIT S.p.A.</t>
         </is>
       </c>
       <c r="B395" t="inlineStr">
@@ -15626,14 +15626,14 @@
       </c>
       <c r="C395" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="396">
       <c r="A396" t="inlineStr">
         <is>
-          <t>RECORDATI S.p.A.</t>
+          <t>TREVI - Finanziaria Industriale S.p.A.</t>
         </is>
       </c>
       <c r="B396" t="inlineStr">
@@ -15643,14 +15643,14 @@
       </c>
       <c r="C396" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="397">
       <c r="A397" t="inlineStr">
         <is>
-          <t>Neodecortech S.p.A.</t>
+          <t>Fiera Milano S.p.A</t>
         </is>
       </c>
       <c r="B397" t="inlineStr">
@@ -15660,7 +15660,7 @@
       </c>
       <c r="C397" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
@@ -15684,7 +15684,7 @@
     <row r="399">
       <c r="A399" t="inlineStr">
         <is>
-          <t>Snam S.p.A.</t>
+          <t>GEOX S.p.A.</t>
         </is>
       </c>
       <c r="B399" t="inlineStr">
@@ -15701,7 +15701,7 @@
     <row r="400">
       <c r="A400" t="inlineStr">
         <is>
-          <t>TREVI - Finanziaria Industriale S.p.A.</t>
+          <t>IMMSI S.p.A.</t>
         </is>
       </c>
       <c r="B400" t="inlineStr">
@@ -15711,14 +15711,14 @@
       </c>
       <c r="C400" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="401">
       <c r="A401" t="inlineStr">
         <is>
-          <t>IMMSI S.p.A.</t>
+          <t>RCS MediaGroup S.p.A.</t>
         </is>
       </c>
       <c r="B401" t="inlineStr">
@@ -15735,7 +15735,7 @@
     <row r="402">
       <c r="A402" t="inlineStr">
         <is>
-          <t>HERA S.p.A.</t>
+          <t>RAI WAY S.p.A.</t>
         </is>
       </c>
       <c r="B402" t="inlineStr">
@@ -15752,7 +15752,7 @@
     <row r="403">
       <c r="A403" t="inlineStr">
         <is>
-          <t>GEOX S.p.A.</t>
+          <t>Pattern S.p.A.</t>
         </is>
       </c>
       <c r="B403" t="inlineStr">
@@ -15769,7 +15769,7 @@
     <row r="404">
       <c r="A404" t="inlineStr">
         <is>
-          <t>GEOX S.p.A.</t>
+          <t>POLIGRAFICI PRINTING S.p.A.</t>
         </is>
       </c>
       <c r="B404" t="inlineStr">
@@ -15779,14 +15779,14 @@
       </c>
       <c r="C404" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="405">
       <c r="A405" t="inlineStr">
         <is>
-          <t>Fiera Milano S.p.A</t>
+          <t>Neodecortech S.p.A.</t>
         </is>
       </c>
       <c r="B405" t="inlineStr">
@@ -15803,7 +15803,7 @@
     <row r="406">
       <c r="A406" t="inlineStr">
         <is>
-          <t>Fiera Milano S.p.A</t>
+          <t>NEWPRINCES</t>
         </is>
       </c>
       <c r="B406" t="inlineStr">
@@ -15813,14 +15813,14 @@
       </c>
       <c r="C406" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="407">
       <c r="A407" t="inlineStr">
         <is>
-          <t>INWIT S.p.A.</t>
+          <t>HERA S.p.A.</t>
         </is>
       </c>
       <c r="B407" t="inlineStr">
@@ -15830,14 +15830,14 @@
       </c>
       <c r="C407" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="408">
       <c r="A408" t="inlineStr">
         <is>
-          <t>ITALMOBILIARE S.p.A.</t>
+          <t>ESPE S.p.A.</t>
         </is>
       </c>
       <c r="B408" t="inlineStr">
@@ -15847,14 +15847,14 @@
       </c>
       <c r="C408" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Bod Annual Report</t>
         </is>
       </c>
     </row>
     <row r="409">
       <c r="A409" t="inlineStr">
         <is>
-          <t>Esprinet S.p.A.</t>
+          <t>Digital Value S.p.A.</t>
         </is>
       </c>
       <c r="B409" t="inlineStr">
@@ -15864,14 +15864,14 @@
       </c>
       <c r="C409" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="410">
       <c r="A410" t="inlineStr">
         <is>
-          <t>NEWPRINCES</t>
+          <t>DIGITAL BROS S.p.A.</t>
         </is>
       </c>
       <c r="B410" t="inlineStr">
@@ -15881,14 +15881,14 @@
       </c>
       <c r="C410" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="411">
       <c r="A411" t="inlineStr">
         <is>
-          <t>ZEST S.p.A.</t>
+          <t>CENTRALE DEL LATTE D'ITALIA S.p.A.</t>
         </is>
       </c>
       <c r="B411" t="inlineStr">
@@ -15905,7 +15905,7 @@
     <row r="412">
       <c r="A412" t="inlineStr">
         <is>
-          <t>WIIT S.p.A.</t>
+          <t>Esprinet S.p.A.</t>
         </is>
       </c>
       <c r="B412" t="inlineStr">
@@ -15922,7 +15922,7 @@
     <row r="413">
       <c r="A413" t="inlineStr">
         <is>
-          <t>WIIT S.p.A.</t>
+          <t>NEWPRINCES</t>
         </is>
       </c>
       <c r="B413" t="inlineStr">
@@ -15939,7 +15939,7 @@
     <row r="414">
       <c r="A414" t="inlineStr">
         <is>
-          <t>MFE-MEDIAFOREUROPE N.V.</t>
+          <t>INWIT S.p.A.</t>
         </is>
       </c>
       <c r="B414" t="inlineStr">
@@ -15949,14 +15949,14 @@
       </c>
       <c r="C414" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="415">
       <c r="A415" t="inlineStr">
         <is>
-          <t>Acinque S.p.A.</t>
+          <t>ITALMOBILIARE S.p.A.</t>
         </is>
       </c>
       <c r="B415" t="inlineStr">
@@ -15973,7 +15973,7 @@
     <row r="416">
       <c r="A416" t="inlineStr">
         <is>
-          <t>B&amp;C SPEAKERS S.p.A.</t>
+          <t>Snam S.p.A.</t>
         </is>
       </c>
       <c r="B416" t="inlineStr">
@@ -15990,7 +15990,7 @@
     <row r="417">
       <c r="A417" t="inlineStr">
         <is>
-          <t>BUZZI S.p.A.</t>
+          <t>CALEFFI S.p.A.</t>
         </is>
       </c>
       <c r="B417" t="inlineStr">
@@ -16000,7 +16000,7 @@
       </c>
       <c r="C417" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
@@ -16017,14 +16017,14 @@
       </c>
       <c r="C418" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="419">
       <c r="A419" t="inlineStr">
         <is>
-          <t>CALEFFI S.p.A.</t>
+          <t>ARNOLDO MONDADORI EDITORE S.p.A.</t>
         </is>
       </c>
       <c r="B419" t="inlineStr">
@@ -16034,14 +16034,14 @@
       </c>
       <c r="C419" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="420">
       <c r="A420" t="inlineStr">
         <is>
-          <t>CENTRALE DEL LATTE D'ITALIA S.p.A.</t>
+          <t>Acinque S.p.A.</t>
         </is>
       </c>
       <c r="B420" t="inlineStr">
@@ -16058,7 +16058,7 @@
     <row r="421">
       <c r="A421" t="inlineStr">
         <is>
-          <t>DIGITAL BROS S.p.A.</t>
+          <t>MFE-MEDIAFOREUROPE N.V.</t>
         </is>
       </c>
       <c r="B421" t="inlineStr">
@@ -16075,7 +16075,7 @@
     <row r="422">
       <c r="A422" t="inlineStr">
         <is>
-          <t>Digital Value S.p.A.</t>
+          <t>BUZZI S.p.A.</t>
         </is>
       </c>
       <c r="B422" t="inlineStr">
@@ -16092,7 +16092,7 @@
     <row r="423">
       <c r="A423" t="inlineStr">
         <is>
-          <t>ESPE S.p.A.</t>
+          <t>BUZZI S.p.A.</t>
         </is>
       </c>
       <c r="B423" t="inlineStr">
@@ -16102,14 +16102,14 @@
       </c>
       <c r="C423" t="inlineStr">
         <is>
-          <t>Bod Annual Report</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="424">
       <c r="A424" t="inlineStr">
         <is>
-          <t>BUZZI S.p.A.</t>
+          <t>B&amp;C SPEAKERS S.p.A.</t>
         </is>
       </c>
       <c r="B424" t="inlineStr">
@@ -16126,7 +16126,7 @@
     <row r="425">
       <c r="A425" t="inlineStr">
         <is>
-          <t>Neodecortech S.p.A.</t>
+          <t>DATALOGIC S.p.A.</t>
         </is>
       </c>
       <c r="B425" t="inlineStr">
@@ -16136,14 +16136,14 @@
       </c>
       <c r="C425" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="426">
       <c r="A426" t="inlineStr">
         <is>
-          <t>SYS-DAT S.p.A.</t>
+          <t>ENAV S.p.A.</t>
         </is>
       </c>
       <c r="B426" t="inlineStr">
@@ -16153,14 +16153,14 @@
       </c>
       <c r="C426" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="427">
       <c r="A427" t="inlineStr">
         <is>
-          <t>Sanlorenzo S.p.A.</t>
+          <t>EQUITA GROUP S.p.A.</t>
         </is>
       </c>
       <c r="B427" t="inlineStr">
@@ -16170,14 +16170,14 @@
       </c>
       <c r="C427" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="428">
       <c r="A428" t="inlineStr">
         <is>
-          <t>TREVI - Finanziaria Industriale S.p.A.</t>
+          <t>ESAUTOMOTION S.p.A.</t>
         </is>
       </c>
       <c r="B428" t="inlineStr">
@@ -16187,14 +16187,14 @@
       </c>
       <c r="C428" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="429">
       <c r="A429" t="inlineStr">
         <is>
-          <t>SOL S.p.A.</t>
+          <t>EUROTECH S.p.A.</t>
         </is>
       </c>
       <c r="B429" t="inlineStr">
@@ -16204,14 +16204,14 @@
       </c>
       <c r="C429" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="430">
       <c r="A430" t="inlineStr">
         <is>
-          <t>SALVATORE FERRAGAMO S.p.A.</t>
+          <t>FINCANTIERI S.p.A.</t>
         </is>
       </c>
       <c r="B430" t="inlineStr">
@@ -16221,14 +16221,14 @@
       </c>
       <c r="C430" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="431">
       <c r="A431" t="inlineStr">
         <is>
-          <t>Industrie Chimiche Forestali S.p.A.</t>
+          <t>CAIRO COMMUNICATION S.p.A.</t>
         </is>
       </c>
       <c r="B431" t="inlineStr">
@@ -16245,7 +16245,7 @@
     <row r="432">
       <c r="A432" t="inlineStr">
         <is>
-          <t>MOLTIPLY GROUP S.p.A.</t>
+          <t>CAREL INDUSTRIES S.p.A.</t>
         </is>
       </c>
       <c r="B432" t="inlineStr">
@@ -16262,7 +16262,7 @@
     <row r="433">
       <c r="A433" t="inlineStr">
         <is>
-          <t>OSAI Automation System S.p.A.</t>
+          <t>CEMBRE S.p.A.</t>
         </is>
       </c>
       <c r="B433" t="inlineStr">
@@ -16272,14 +16272,14 @@
       </c>
       <c r="C433" t="inlineStr">
         <is>
-          <t>Half Year Report</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="434">
       <c r="A434" t="inlineStr">
         <is>
-          <t>WEBUILD S.p.A.</t>
+          <t>ITALIAN EXHIBITION GROUP S.p.A.</t>
         </is>
       </c>
       <c r="B434" t="inlineStr">
@@ -16296,7 +16296,7 @@
     <row r="435">
       <c r="A435" t="inlineStr">
         <is>
-          <t>PROMOTICA S.p.A.</t>
+          <t>Gabetti Property Solutions S.p.A.</t>
         </is>
       </c>
       <c r="B435" t="inlineStr">
@@ -16306,14 +16306,14 @@
       </c>
       <c r="C435" t="inlineStr">
         <is>
-          <t>Bod Annual Report</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="436">
       <c r="A436" t="inlineStr">
         <is>
-          <t>REVO Insurance S.p.A.</t>
+          <t>GEFRAN S.p.A.</t>
         </is>
       </c>
       <c r="B436" t="inlineStr">
@@ -16330,7 +16330,7 @@
     <row r="437">
       <c r="A437" t="inlineStr">
         <is>
-          <t>SABAF S.p.A.</t>
+          <t>FNM S.p.A.</t>
         </is>
       </c>
       <c r="B437" t="inlineStr">
@@ -16340,14 +16340,14 @@
       </c>
       <c r="C437" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="438">
       <c r="A438" t="inlineStr">
         <is>
-          <t>SABAF S.p.A.</t>
+          <t>Ferretti S.p.A.</t>
         </is>
       </c>
       <c r="B438" t="inlineStr">
@@ -16357,14 +16357,14 @@
       </c>
       <c r="C438" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="439">
       <c r="A439" t="inlineStr">
         <is>
-          <t>SALVATORE FERRAGAMO S.p.A.</t>
+          <t>First Capital S.p.A.</t>
         </is>
       </c>
       <c r="B439" t="inlineStr">
@@ -16381,7 +16381,7 @@
     <row r="440">
       <c r="A440" t="inlineStr">
         <is>
-          <t>TREVI - Finanziaria Industriale S.p.A.</t>
+          <t>GAROFALO HEALTH CARE S.p.A.</t>
         </is>
       </c>
       <c r="B440" t="inlineStr">
@@ -16398,7 +16398,7 @@
     <row r="441">
       <c r="A441" t="inlineStr">
         <is>
-          <t>A2A S.p.A.</t>
+          <t>Toscana Aeroporti S.p.A.</t>
         </is>
       </c>
       <c r="B441" t="inlineStr">
@@ -16415,7 +16415,7 @@
     <row r="442">
       <c r="A442" t="inlineStr">
         <is>
-          <t>ACEA S.p.A.</t>
+          <t>Unipol S.p.A.</t>
         </is>
       </c>
       <c r="B442" t="inlineStr">
@@ -16432,7 +16432,7 @@
     <row r="443">
       <c r="A443" t="inlineStr">
         <is>
-          <t>Alerion Clean Power S.p.A.</t>
+          <t>WEBUILD S.p.A.</t>
         </is>
       </c>
       <c r="B443" t="inlineStr">
@@ -16449,7 +16449,7 @@
     <row r="444">
       <c r="A444" t="inlineStr">
         <is>
-          <t>Orsero S.p.A.</t>
+          <t>doValue S.p.A.</t>
         </is>
       </c>
       <c r="B444" t="inlineStr">
@@ -16466,7 +16466,7 @@
     <row r="445">
       <c r="A445" t="inlineStr">
         <is>
-          <t>TXT E-SOLUTIONS S.p.A.</t>
+          <t>GVS S.p.A.</t>
         </is>
       </c>
       <c r="B445" t="inlineStr">
@@ -16483,7 +16483,7 @@
     <row r="446">
       <c r="A446" t="inlineStr">
         <is>
-          <t>Altea Green Power S.p.A.</t>
+          <t>F.I.L.A. S.p.A.</t>
         </is>
       </c>
       <c r="B446" t="inlineStr">
@@ -16500,7 +16500,7 @@
     <row r="447">
       <c r="A447" t="inlineStr">
         <is>
-          <t>Tinexta S.p.A.</t>
+          <t>CIRCLE S.p.A.</t>
         </is>
       </c>
       <c r="B447" t="inlineStr">
@@ -16517,7 +16517,7 @@
     <row r="448">
       <c r="A448" t="inlineStr">
         <is>
-          <t>CIRCLE S.p.A.</t>
+          <t>Tinexta S.p.A.</t>
         </is>
       </c>
       <c r="B448" t="inlineStr">
@@ -16527,14 +16527,14 @@
       </c>
       <c r="C448" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="449">
       <c r="A449" t="inlineStr">
         <is>
-          <t>CEMBRE S.p.A.</t>
+          <t>Aquafil S.p.A.</t>
         </is>
       </c>
       <c r="B449" t="inlineStr">
@@ -16551,7 +16551,7 @@
     <row r="450">
       <c r="A450" t="inlineStr">
         <is>
-          <t>CAREL INDUSTRIES S.p.A.</t>
+          <t>BIESSE S.p.A.</t>
         </is>
       </c>
       <c r="B450" t="inlineStr">
@@ -16568,7 +16568,7 @@
     <row r="451">
       <c r="A451" t="inlineStr">
         <is>
-          <t>CAIRO COMMUNICATION S.p.A.</t>
+          <t>Orsero S.p.A.</t>
         </is>
       </c>
       <c r="B451" t="inlineStr">
@@ -16585,7 +16585,7 @@
     <row r="452">
       <c r="A452" t="inlineStr">
         <is>
-          <t>Aquafil S.p.A.</t>
+          <t>Tinexta S.p.A.</t>
         </is>
       </c>
       <c r="B452" t="inlineStr">
@@ -16602,7 +16602,7 @@
     <row r="453">
       <c r="A453" t="inlineStr">
         <is>
-          <t>BIESSE S.p.A.</t>
+          <t>Technoprobe S.p.A.</t>
         </is>
       </c>
       <c r="B453" t="inlineStr">
@@ -16619,7 +16619,7 @@
     <row r="454">
       <c r="A454" t="inlineStr">
         <is>
-          <t>F.I.L.A. S.p.A.</t>
+          <t>TXT E-SOLUTIONS S.p.A.</t>
         </is>
       </c>
       <c r="B454" t="inlineStr">
@@ -16636,7 +16636,7 @@
     <row r="455">
       <c r="A455" t="inlineStr">
         <is>
-          <t>FINCANTIERI S.p.A.</t>
+          <t>TREVI - Finanziaria Industriale S.p.A.</t>
         </is>
       </c>
       <c r="B455" t="inlineStr">
@@ -16646,14 +16646,14 @@
       </c>
       <c r="C455" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="456">
       <c r="A456" t="inlineStr">
         <is>
-          <t>FNM S.p.A.</t>
+          <t>TREVI - Finanziaria Industriale S.p.A.</t>
         </is>
       </c>
       <c r="B456" t="inlineStr">
@@ -16663,14 +16663,14 @@
       </c>
       <c r="C456" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="457">
       <c r="A457" t="inlineStr">
         <is>
-          <t>Ferretti S.p.A.</t>
+          <t>Altea Green Power S.p.A.</t>
         </is>
       </c>
       <c r="B457" t="inlineStr">
@@ -16680,14 +16680,14 @@
       </c>
       <c r="C457" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="458">
       <c r="A458" t="inlineStr">
         <is>
-          <t>First Capital S.p.A.</t>
+          <t>Sanlorenzo S.p.A.</t>
         </is>
       </c>
       <c r="B458" t="inlineStr">
@@ -16697,14 +16697,14 @@
       </c>
       <c r="C458" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="459">
       <c r="A459" t="inlineStr">
         <is>
-          <t>GAROFALO HEALTH CARE S.p.A.</t>
+          <t>SOL S.p.A.</t>
         </is>
       </c>
       <c r="B459" t="inlineStr">
@@ -16714,14 +16714,14 @@
       </c>
       <c r="C459" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="460">
       <c r="A460" t="inlineStr">
         <is>
-          <t>GEFRAN S.p.A.</t>
+          <t>CY4Gate S.p.A.</t>
         </is>
       </c>
       <c r="B460" t="inlineStr">
@@ -16738,7 +16738,7 @@
     <row r="461">
       <c r="A461" t="inlineStr">
         <is>
-          <t>GVS S.p.A.</t>
+          <t>SALVATORE FERRAGAMO S.p.A.</t>
         </is>
       </c>
       <c r="B461" t="inlineStr">
@@ -16748,14 +16748,14 @@
       </c>
       <c r="C461" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="462">
       <c r="A462" t="inlineStr">
         <is>
-          <t>Alfonsino S.p.A.</t>
+          <t>SALVATORE FERRAGAMO S.p.A.</t>
         </is>
       </c>
       <c r="B462" t="inlineStr">
@@ -16772,7 +16772,7 @@
     <row r="463">
       <c r="A463" t="inlineStr">
         <is>
-          <t>Gabetti Property Solutions S.p.A.</t>
+          <t>SABAF S.p.A.</t>
         </is>
       </c>
       <c r="B463" t="inlineStr">
@@ -16789,7 +16789,7 @@
     <row r="464">
       <c r="A464" t="inlineStr">
         <is>
-          <t>ITALIAN EXHIBITION GROUP S.p.A.</t>
+          <t>SABAF S.p.A.</t>
         </is>
       </c>
       <c r="B464" t="inlineStr">
@@ -16799,14 +16799,14 @@
       </c>
       <c r="C464" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="465">
       <c r="A465" t="inlineStr">
         <is>
-          <t>Technoprobe S.p.A.</t>
+          <t>REVO Insurance S.p.A.</t>
         </is>
       </c>
       <c r="B465" t="inlineStr">
@@ -16823,7 +16823,7 @@
     <row r="466">
       <c r="A466" t="inlineStr">
         <is>
-          <t>DATALOGIC S.p.A.</t>
+          <t>PROMOTICA S.p.A.</t>
         </is>
       </c>
       <c r="B466" t="inlineStr">
@@ -16833,14 +16833,14 @@
       </c>
       <c r="C466" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Bod Annual Report</t>
         </is>
       </c>
     </row>
     <row r="467">
       <c r="A467" t="inlineStr">
         <is>
-          <t>CY4Gate S.p.A.</t>
+          <t>SYS-DAT S.p.A.</t>
         </is>
       </c>
       <c r="B467" t="inlineStr">
@@ -16857,7 +16857,7 @@
     <row r="468">
       <c r="A468" t="inlineStr">
         <is>
-          <t>EQUITA GROUP S.p.A.</t>
+          <t>Alfonsino S.p.A.</t>
         </is>
       </c>
       <c r="B468" t="inlineStr">
@@ -16874,7 +16874,7 @@
     <row r="469">
       <c r="A469" t="inlineStr">
         <is>
-          <t>Unipol S.p.A.</t>
+          <t>OSAI Automation System S.p.A.</t>
         </is>
       </c>
       <c r="B469" t="inlineStr">
@@ -16884,14 +16884,14 @@
       </c>
       <c r="C469" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Half Year Report</t>
         </is>
       </c>
     </row>
     <row r="470">
       <c r="A470" t="inlineStr">
         <is>
-          <t>Toscana Aeroporti S.p.A.</t>
+          <t>ACEA S.p.A.</t>
         </is>
       </c>
       <c r="B470" t="inlineStr">
@@ -16908,7 +16908,7 @@
     <row r="471">
       <c r="A471" t="inlineStr">
         <is>
-          <t>Tinexta S.p.A.</t>
+          <t>A2A S.p.A.</t>
         </is>
       </c>
       <c r="B471" t="inlineStr">
@@ -16918,14 +16918,14 @@
       </c>
       <c r="C471" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="472">
       <c r="A472" t="inlineStr">
         <is>
-          <t>EUROTECH S.p.A.</t>
+          <t>Alerion Clean Power S.p.A.</t>
         </is>
       </c>
       <c r="B472" t="inlineStr">
@@ -16942,7 +16942,7 @@
     <row r="473">
       <c r="A473" t="inlineStr">
         <is>
-          <t>ESAUTOMOTION S.p.A.</t>
+          <t>Industrie Chimiche Forestali S.p.A.</t>
         </is>
       </c>
       <c r="B473" t="inlineStr">
@@ -16959,7 +16959,7 @@
     <row r="474">
       <c r="A474" t="inlineStr">
         <is>
-          <t>ENAV S.p.A.</t>
+          <t>Neodecortech S.p.A.</t>
         </is>
       </c>
       <c r="B474" t="inlineStr">
@@ -16969,14 +16969,14 @@
       </c>
       <c r="C474" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="475">
       <c r="A475" t="inlineStr">
         <is>
-          <t>doValue S.p.A.</t>
+          <t>MOLTIPLY GROUP S.p.A.</t>
         </is>
       </c>
       <c r="B475" t="inlineStr">
@@ -16993,7 +16993,7 @@
     <row r="476">
       <c r="A476" t="inlineStr">
         <is>
-          <t>ERG S.p.A.</t>
+          <t>VNE S.p.A.</t>
         </is>
       </c>
       <c r="B476" t="inlineStr">
@@ -17010,7 +17010,7 @@
     <row r="477">
       <c r="A477" t="inlineStr">
         <is>
-          <t>TAMBURI INVESTMENT PARTNERS S.p.A.</t>
+          <t>VINCENZO ZUCCHI S.p.A.</t>
         </is>
       </c>
       <c r="B477" t="inlineStr">
@@ -17020,14 +17020,14 @@
       </c>
       <c r="C477" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Bod Annual Report</t>
         </is>
       </c>
     </row>
     <row r="478">
       <c r="A478" t="inlineStr">
         <is>
-          <t>MARR S.p.A.</t>
+          <t>TAMBURI INVESTMENT PARTNERS S.p.A.</t>
         </is>
       </c>
       <c r="B478" t="inlineStr">
@@ -17037,14 +17037,14 @@
       </c>
       <c r="C478" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="479">
       <c r="A479" t="inlineStr">
         <is>
-          <t>IRCE s.p.a</t>
+          <t>SOGES GROUP S.p.A.</t>
         </is>
       </c>
       <c r="B479" t="inlineStr">
@@ -17061,7 +17061,7 @@
     <row r="480">
       <c r="A480" t="inlineStr">
         <is>
-          <t>INTERPUMP GROUP S.p.A.</t>
+          <t>REPLY S.p.A.</t>
         </is>
       </c>
       <c r="B480" t="inlineStr">
@@ -17078,7 +17078,7 @@
     <row r="481">
       <c r="A481" t="inlineStr">
         <is>
-          <t>GVS S.p.A.</t>
+          <t>Praexidia Industrie Strategiche S.p.A.</t>
         </is>
       </c>
       <c r="B481" t="inlineStr">
@@ -17088,14 +17088,14 @@
       </c>
       <c r="C481" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Bod Annual Report</t>
         </is>
       </c>
     </row>
     <row r="482">
       <c r="A482" t="inlineStr">
         <is>
-          <t>Ferretti S.p.A.</t>
+          <t>AEROPORTO GUGLIELMO MARCONI DI BOLOGNA S.p.A.</t>
         </is>
       </c>
       <c r="B482" t="inlineStr">
@@ -17105,14 +17105,14 @@
       </c>
       <c r="C482" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="483">
       <c r="A483" t="inlineStr">
         <is>
-          <t>MARR S.p.A.</t>
+          <t>AEROPORTO GUGLIELMO MARCONI DI BOLOGNA S.p.A.</t>
         </is>
       </c>
       <c r="B483" t="inlineStr">
@@ -17129,7 +17129,7 @@
     <row r="484">
       <c r="A484" t="inlineStr">
         <is>
-          <t>AEROPORTO GUGLIELMO MARCONI DI BOLOGNA S.p.A.</t>
+          <t>CLABO S.p.A.</t>
         </is>
       </c>
       <c r="B484" t="inlineStr">
@@ -17139,14 +17139,14 @@
       </c>
       <c r="C484" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="485">
       <c r="A485" t="inlineStr">
         <is>
-          <t>CLABO S.p.A.</t>
+          <t>CLASS EDITORI S.p.A.</t>
         </is>
       </c>
       <c r="B485" t="inlineStr">
@@ -17163,7 +17163,7 @@
     <row r="486">
       <c r="A486" t="inlineStr">
         <is>
-          <t>AEROPORTO GUGLIELMO MARCONI DI BOLOGNA S.p.A.</t>
+          <t>Renovalo S.p.A.</t>
         </is>
       </c>
       <c r="B486" t="inlineStr">
@@ -17180,7 +17180,7 @@
     <row r="487">
       <c r="A487" t="inlineStr">
         <is>
-          <t>SOGES GROUP S.p.A.</t>
+          <t>ECOSUNTEK S.p.A.</t>
         </is>
       </c>
       <c r="B487" t="inlineStr">
@@ -17197,7 +17197,7 @@
     <row r="488">
       <c r="A488" t="inlineStr">
         <is>
-          <t>CLASS EDITORI S.p.A.</t>
+          <t>CY4Gate S.p.A.</t>
         </is>
       </c>
       <c r="B488" t="inlineStr">
@@ -17207,14 +17207,14 @@
       </c>
       <c r="C488" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="489">
       <c r="A489" t="inlineStr">
         <is>
-          <t>CY4Gate S.p.A.</t>
+          <t>MARR S.p.A.</t>
         </is>
       </c>
       <c r="B489" t="inlineStr">
@@ -17224,14 +17224,14 @@
       </c>
       <c r="C489" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="490">
       <c r="A490" t="inlineStr">
         <is>
-          <t>ECOSUNTEK S.p.A.</t>
+          <t>MARR S.p.A.</t>
         </is>
       </c>
       <c r="B490" t="inlineStr">
@@ -17241,14 +17241,14 @@
       </c>
       <c r="C490" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="491">
       <c r="A491" t="inlineStr">
         <is>
-          <t>ERG S.p.A.</t>
+          <t>IRCE s.p.a</t>
         </is>
       </c>
       <c r="B491" t="inlineStr">
@@ -17258,14 +17258,14 @@
       </c>
       <c r="C491" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="492">
       <c r="A492" t="inlineStr">
         <is>
-          <t>Praexidia Industrie Strategiche S.p.A.</t>
+          <t>INTERPUMP GROUP S.p.A.</t>
         </is>
       </c>
       <c r="B492" t="inlineStr">
@@ -17275,14 +17275,14 @@
       </c>
       <c r="C492" t="inlineStr">
         <is>
-          <t>Bod Annual Report</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="493">
       <c r="A493" t="inlineStr">
         <is>
-          <t>REPLY S.p.A.</t>
+          <t>GVS S.p.A.</t>
         </is>
       </c>
       <c r="B493" t="inlineStr">
@@ -17292,14 +17292,14 @@
       </c>
       <c r="C493" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="494">
       <c r="A494" t="inlineStr">
         <is>
-          <t>Renovalo S.p.A.</t>
+          <t>VNE S.p.A.</t>
         </is>
       </c>
       <c r="B494" t="inlineStr">
@@ -17309,14 +17309,14 @@
       </c>
       <c r="C494" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Bod Annual Report</t>
         </is>
       </c>
     </row>
     <row r="495">
       <c r="A495" t="inlineStr">
         <is>
-          <t>VNE S.p.A.</t>
+          <t>FIDIA S.p.A</t>
         </is>
       </c>
       <c r="B495" t="inlineStr">
@@ -17326,14 +17326,14 @@
       </c>
       <c r="C495" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Bod Annual Report</t>
         </is>
       </c>
     </row>
     <row r="496">
       <c r="A496" t="inlineStr">
         <is>
-          <t>VNE S.p.A.</t>
+          <t>Ferretti S.p.A.</t>
         </is>
       </c>
       <c r="B496" t="inlineStr">
@@ -17343,14 +17343,14 @@
       </c>
       <c r="C496" t="inlineStr">
         <is>
-          <t>Bod Annual Report</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="497">
       <c r="A497" t="inlineStr">
         <is>
-          <t>VINCENZO ZUCCHI S.p.A.</t>
+          <t>ERG S.p.A.</t>
         </is>
       </c>
       <c r="B497" t="inlineStr">
@@ -17360,14 +17360,14 @@
       </c>
       <c r="C497" t="inlineStr">
         <is>
-          <t>Bod Annual Report</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="498">
       <c r="A498" t="inlineStr">
         <is>
-          <t>EL.EN. S.p.A.</t>
+          <t>ERG S.p.A.</t>
         </is>
       </c>
       <c r="B498" t="inlineStr">
@@ -17377,14 +17377,14 @@
       </c>
       <c r="C498" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="499">
       <c r="A499" t="inlineStr">
         <is>
-          <t>FIDIA S.p.A</t>
+          <t>EL.EN. S.p.A.</t>
         </is>
       </c>
       <c r="B499" t="inlineStr">
@@ -17394,14 +17394,14 @@
       </c>
       <c r="C499" t="inlineStr">
         <is>
-          <t>Bod Annual Report</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="500">
       <c r="A500" t="inlineStr">
         <is>
-          <t>EuroGroup Laminations S.p.A.</t>
+          <t>SYS-DAT S.p.A.</t>
         </is>
       </c>
       <c r="B500" t="inlineStr">
@@ -17411,14 +17411,14 @@
       </c>
       <c r="C500" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="501">
       <c r="A501" t="inlineStr">
         <is>
-          <t>BESTBE HOLDING S.p.A.</t>
+          <t>GREEN OLEO S.p.A</t>
         </is>
       </c>
       <c r="B501" t="inlineStr">
@@ -17428,14 +17428,14 @@
       </c>
       <c r="C501" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="502">
       <c r="A502" t="inlineStr">
         <is>
-          <t>GREEN OLEO S.p.A</t>
+          <t>OMER S.p.A.</t>
         </is>
       </c>
       <c r="B502" t="inlineStr">
@@ -17452,7 +17452,7 @@
     <row r="503">
       <c r="A503" t="inlineStr">
         <is>
-          <t>SYS-DAT S.p.A.</t>
+          <t>BESTBE HOLDING S.p.A.</t>
         </is>
       </c>
       <c r="B503" t="inlineStr">
@@ -17462,14 +17462,14 @@
       </c>
       <c r="C503" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="504">
       <c r="A504" t="inlineStr">
         <is>
-          <t>OMER S.p.A.</t>
+          <t>EuroGroup Laminations S.p.A.</t>
         </is>
       </c>
       <c r="B504" t="inlineStr">
@@ -17486,7 +17486,7 @@
     <row r="505">
       <c r="A505" t="inlineStr">
         <is>
-          <t>SOLUTIONS CAPITAL MANAGEMENT SIM S.p.A.</t>
+          <t>Officina Stellare S.p.A.</t>
         </is>
       </c>
       <c r="B505" t="inlineStr">
@@ -17496,14 +17496,14 @@
       </c>
       <c r="C505" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Bod Annual Report</t>
         </is>
       </c>
     </row>
     <row r="506">
       <c r="A506" t="inlineStr">
         <is>
-          <t>Officina Stellare S.p.A.</t>
+          <t>SOLUTIONS CAPITAL MANAGEMENT SIM S.p.A.</t>
         </is>
       </c>
       <c r="B506" t="inlineStr">
@@ -17513,14 +17513,14 @@
       </c>
       <c r="C506" t="inlineStr">
         <is>
-          <t>Bod Annual Report</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="507">
       <c r="A507" t="inlineStr">
         <is>
-          <t>eVISO S.p.A.</t>
+          <t>OPS Italia S.p.A.</t>
         </is>
       </c>
       <c r="B507" t="inlineStr">
@@ -17530,14 +17530,14 @@
       </c>
       <c r="C507" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Bod Annual Report</t>
         </is>
       </c>
     </row>
     <row r="508">
       <c r="A508" t="inlineStr">
         <is>
-          <t>Svas Biosana S.p.A.</t>
+          <t>Energy Time S.p.A.</t>
         </is>
       </c>
       <c r="B508" t="inlineStr">
@@ -17547,14 +17547,14 @@
       </c>
       <c r="C508" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="509">
       <c r="A509" t="inlineStr">
         <is>
-          <t>OPS Italia S.p.A.</t>
+          <t>Svas Biosana S.p.A.</t>
         </is>
       </c>
       <c r="B509" t="inlineStr">
@@ -17564,14 +17564,14 @@
       </c>
       <c r="C509" t="inlineStr">
         <is>
-          <t>Bod Annual Report</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="510">
       <c r="A510" t="inlineStr">
         <is>
-          <t>Energy Time S.p.A.</t>
+          <t>eVISO S.p.A.</t>
         </is>
       </c>
       <c r="B510" t="inlineStr">
@@ -17581,7 +17581,7 @@
       </c>
       <c r="C510" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
@@ -17622,7 +17622,7 @@
     <row r="513">
       <c r="A513" t="inlineStr">
         <is>
-          <t>Stellantis N.V.</t>
+          <t>ASSICURAZIONI GENERALI S.p.A.</t>
         </is>
       </c>
       <c r="B513" t="inlineStr">
@@ -17639,7 +17639,7 @@
     <row r="514">
       <c r="A514" t="inlineStr">
         <is>
-          <t>ASSICURAZIONI GENERALI S.p.A.</t>
+          <t>DOTSTAY S.p.A.</t>
         </is>
       </c>
       <c r="B514" t="inlineStr">
@@ -17649,14 +17649,14 @@
       </c>
       <c r="C514" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Bod Annual Report</t>
         </is>
       </c>
     </row>
     <row r="515">
       <c r="A515" t="inlineStr">
         <is>
-          <t>DOTSTAY S.p.A.</t>
+          <t>EXPERT.AI S.p.A.</t>
         </is>
       </c>
       <c r="B515" t="inlineStr">
@@ -17673,7 +17673,7 @@
     <row r="516">
       <c r="A516" t="inlineStr">
         <is>
-          <t>IREN S.p.A.</t>
+          <t>IDNTT S.A.</t>
         </is>
       </c>
       <c r="B516" t="inlineStr">
@@ -17683,14 +17683,14 @@
       </c>
       <c r="C516" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Bod Annual Report</t>
         </is>
       </c>
     </row>
     <row r="517">
       <c r="A517" t="inlineStr">
         <is>
-          <t>EXPERT.AI S.p.A.</t>
+          <t>IREN S.p.A.</t>
         </is>
       </c>
       <c r="B517" t="inlineStr">
@@ -17700,14 +17700,14 @@
       </c>
       <c r="C517" t="inlineStr">
         <is>
-          <t>Bod Annual Report</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="518">
       <c r="A518" t="inlineStr">
         <is>
-          <t>Met.Extra Group S.p.A.</t>
+          <t>Laboratorio Farmaceutico Erfo S.p.A.</t>
         </is>
       </c>
       <c r="B518" t="inlineStr">
@@ -17717,7 +17717,7 @@
       </c>
       <c r="C518" t="inlineStr">
         <is>
-          <t>Bod Annual Report</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
@@ -17741,7 +17741,7 @@
     <row r="520">
       <c r="A520" t="inlineStr">
         <is>
-          <t>Laboratorio Farmaceutico Erfo S.p.A.</t>
+          <t>Met.Extra Group S.p.A.</t>
         </is>
       </c>
       <c r="B520" t="inlineStr">
@@ -17751,14 +17751,14 @@
       </c>
       <c r="C520" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Bod Annual Report</t>
         </is>
       </c>
     </row>
     <row r="521">
       <c r="A521" t="inlineStr">
         <is>
-          <t>IDNTT S.A.</t>
+          <t>Sanlorenzo S.p.A.</t>
         </is>
       </c>
       <c r="B521" t="inlineStr">
@@ -17768,14 +17768,14 @@
       </c>
       <c r="C521" t="inlineStr">
         <is>
-          <t>Bod Annual Report</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="522">
       <c r="A522" t="inlineStr">
         <is>
-          <t>Sanlorenzo S.p.A.</t>
+          <t>Stellantis N.V.</t>
         </is>
       </c>
       <c r="B522" t="inlineStr">
@@ -17809,7 +17809,7 @@
     <row r="524">
       <c r="A524" t="inlineStr">
         <is>
-          <t>Portobello S.p.A.</t>
+          <t>Sanlorenzo S.p.A.</t>
         </is>
       </c>
       <c r="B524" t="inlineStr">
@@ -17819,14 +17819,14 @@
       </c>
       <c r="C524" t="inlineStr">
         <is>
-          <t>Bod Annual Report</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="525">
       <c r="A525" t="inlineStr">
         <is>
-          <t>Farmacosmo S.p.A.</t>
+          <t>BASTOGI S.p.A.</t>
         </is>
       </c>
       <c r="B525" t="inlineStr">
@@ -17836,14 +17836,14 @@
       </c>
       <c r="C525" t="inlineStr">
         <is>
-          <t>Bod Annual Report</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="526">
       <c r="A526" t="inlineStr">
         <is>
-          <t>DHH S.p.A.</t>
+          <t>BRIOSCHI SVILUPPO IMMOBILIARE S.p.A</t>
         </is>
       </c>
       <c r="B526" t="inlineStr">
@@ -17853,14 +17853,14 @@
       </c>
       <c r="C526" t="inlineStr">
         <is>
-          <t>Additional Periodic Financial Information</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="527">
       <c r="A527" t="inlineStr">
         <is>
-          <t>BRIOSCHI SVILUPPO IMMOBILIARE S.p.A</t>
+          <t>DHH S.p.A.</t>
         </is>
       </c>
       <c r="B527" t="inlineStr">
@@ -17870,14 +17870,14 @@
       </c>
       <c r="C527" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Additional Periodic Financial Information</t>
         </is>
       </c>
     </row>
     <row r="528">
       <c r="A528" t="inlineStr">
         <is>
-          <t>BASTOGI S.p.A.</t>
+          <t>Farmacosmo S.p.A.</t>
         </is>
       </c>
       <c r="B528" t="inlineStr">
@@ -17887,14 +17887,14 @@
       </c>
       <c r="C528" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Bod Annual Report</t>
         </is>
       </c>
     </row>
     <row r="529">
       <c r="A529" t="inlineStr">
         <is>
-          <t>Sanlorenzo S.p.A.</t>
+          <t>Portobello S.p.A.</t>
         </is>
       </c>
       <c r="B529" t="inlineStr">
@@ -17904,14 +17904,14 @@
       </c>
       <c r="C529" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Bod Annual Report</t>
         </is>
       </c>
     </row>
     <row r="530">
       <c r="A530" t="inlineStr">
         <is>
-          <t>BASTOGI S.p.A.</t>
+          <t>BRIOSCHI SVILUPPO IMMOBILIARE S.p.A</t>
         </is>
       </c>
       <c r="B530" t="inlineStr">
@@ -17928,7 +17928,7 @@
     <row r="531">
       <c r="A531" t="inlineStr">
         <is>
-          <t>BRIOSCHI SVILUPPO IMMOBILIARE S.p.A</t>
+          <t>BASTOGI S.p.A.</t>
         </is>
       </c>
       <c r="B531" t="inlineStr">
@@ -17945,7 +17945,7 @@
     <row r="532">
       <c r="A532" t="inlineStr">
         <is>
-          <t>COFLE S.p.A.</t>
+          <t>Indel B S.p.A.</t>
         </is>
       </c>
       <c r="B532" t="inlineStr">
@@ -17955,14 +17955,14 @@
       </c>
       <c r="C532" t="inlineStr">
         <is>
-          <t>Bod Annual Report</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="533">
       <c r="A533" t="inlineStr">
         <is>
-          <t>Indel B S.p.A.</t>
+          <t>COFLE S.p.A.</t>
         </is>
       </c>
       <c r="B533" t="inlineStr">
@@ -17972,7 +17972,7 @@
       </c>
       <c r="C533" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Bod Annual Report</t>
         </is>
       </c>
     </row>
@@ -17996,7 +17996,7 @@
     <row r="535">
       <c r="A535" t="inlineStr">
         <is>
-          <t>MEVIM S.p.A.</t>
+          <t>Vivenda Group S.p.A.</t>
         </is>
       </c>
       <c r="B535" t="inlineStr">
@@ -18030,7 +18030,7 @@
     <row r="537">
       <c r="A537" t="inlineStr">
         <is>
-          <t>Sicily by Car S.p.A.</t>
+          <t>DBA GROUP S.p.A.</t>
         </is>
       </c>
       <c r="B537" t="inlineStr">
@@ -18040,14 +18040,14 @@
       </c>
       <c r="C537" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Bod Annual Report</t>
         </is>
       </c>
     </row>
     <row r="538">
       <c r="A538" t="inlineStr">
         <is>
-          <t>Vivenda Group S.p.A.</t>
+          <t>MEVIM S.p.A.</t>
         </is>
       </c>
       <c r="B538" t="inlineStr">
@@ -18064,7 +18064,7 @@
     <row r="539">
       <c r="A539" t="inlineStr">
         <is>
-          <t>DBA GROUP S.p.A.</t>
+          <t>Sicily by Car S.p.A.</t>
         </is>
       </c>
       <c r="B539" t="inlineStr">
@@ -18074,14 +18074,14 @@
       </c>
       <c r="C539" t="inlineStr">
         <is>
-          <t>Bod Annual Report</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="540">
       <c r="A540" t="inlineStr">
         <is>
-          <t>TALEA GROUP</t>
+          <t>ATON Green Storage S.p.A.</t>
         </is>
       </c>
       <c r="B540" t="inlineStr">
@@ -18098,7 +18098,7 @@
     <row r="541">
       <c r="A541" t="inlineStr">
         <is>
-          <t>ATON Green Storage S.p.A.</t>
+          <t>MONDO TV S.p.A.</t>
         </is>
       </c>
       <c r="B541" t="inlineStr">
@@ -18115,7 +18115,7 @@
     <row r="542">
       <c r="A542" t="inlineStr">
         <is>
-          <t>MONDO TV S.p.A.</t>
+          <t>TALEA GROUP</t>
         </is>
       </c>
       <c r="B542" t="inlineStr">
@@ -18149,7 +18149,7 @@
     <row r="544">
       <c r="A544" t="inlineStr">
         <is>
-          <t>AEFFE S.p.A.</t>
+          <t>STMicroelectronics N.V.</t>
         </is>
       </c>
       <c r="B544" t="inlineStr">
@@ -18159,14 +18159,14 @@
       </c>
       <c r="C544" t="inlineStr">
         <is>
-          <t>Bod Annual Report</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="545">
       <c r="A545" t="inlineStr">
         <is>
-          <t>Tenax International S.p.A.</t>
+          <t>CROWDFUNDME S.p.A.</t>
         </is>
       </c>
       <c r="B545" t="inlineStr">
@@ -18176,14 +18176,14 @@
       </c>
       <c r="C545" t="inlineStr">
         <is>
-          <t>Bod Annual Report</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="546">
       <c r="A546" t="inlineStr">
         <is>
-          <t>STMicroelectronics N.V.</t>
+          <t>AEFFE S.p.A.</t>
         </is>
       </c>
       <c r="B546" t="inlineStr">
@@ -18193,14 +18193,14 @@
       </c>
       <c r="C546" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Analyst Presentation</t>
         </is>
       </c>
     </row>
     <row r="547">
       <c r="A547" t="inlineStr">
         <is>
-          <t>CROWDFUNDME S.p.A.</t>
+          <t>AEFFE S.p.A.</t>
         </is>
       </c>
       <c r="B547" t="inlineStr">
@@ -18210,14 +18210,14 @@
       </c>
       <c r="C547" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Bod Annual Report</t>
         </is>
       </c>
     </row>
     <row r="548">
       <c r="A548" t="inlineStr">
         <is>
-          <t>AEFFE S.p.A.</t>
+          <t>Tenax International S.p.A.</t>
         </is>
       </c>
       <c r="B548" t="inlineStr">
@@ -18227,14 +18227,14 @@
       </c>
       <c r="C548" t="inlineStr">
         <is>
-          <t>Analyst Presentation</t>
+          <t>Bod Annual Report</t>
         </is>
       </c>
     </row>
     <row r="549">
       <c r="A549" t="inlineStr">
         <is>
-          <t>CROWDFUNDME S.p.A.</t>
+          <t>FAE Technology Società Benefit S.p.A.</t>
         </is>
       </c>
       <c r="B549" t="inlineStr">
@@ -18251,7 +18251,7 @@
     <row r="550">
       <c r="A550" t="inlineStr">
         <is>
-          <t>Casta Diva Group S.p.A.</t>
+          <t>CROWDFUNDME S.p.A.</t>
         </is>
       </c>
       <c r="B550" t="inlineStr">
@@ -18261,7 +18261,7 @@
       </c>
       <c r="C550" t="inlineStr">
         <is>
-          <t>Bod Annual Report</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
@@ -18285,7 +18285,7 @@
     <row r="552">
       <c r="A552" t="inlineStr">
         <is>
-          <t>FAE Technology Società Benefit S.p.A.</t>
+          <t>Vantea Smart S.p.A.</t>
         </is>
       </c>
       <c r="B552" t="inlineStr">
@@ -18302,7 +18302,7 @@
     <row r="553">
       <c r="A553" t="inlineStr">
         <is>
-          <t>OPS Retail S.p.A.</t>
+          <t>Seri Industrial S.p.A.</t>
         </is>
       </c>
       <c r="B553" t="inlineStr">
@@ -18312,14 +18312,14 @@
       </c>
       <c r="C553" t="inlineStr">
         <is>
-          <t>Bod Annual Report</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="554">
       <c r="A554" t="inlineStr">
         <is>
-          <t>OSAI Automation System S.p.A.</t>
+          <t>Renovalo S.p.A.</t>
         </is>
       </c>
       <c r="B554" t="inlineStr">
@@ -18329,14 +18329,14 @@
       </c>
       <c r="C554" t="inlineStr">
         <is>
-          <t>Bod Annual Report</t>
+          <t>Annual General Meeting</t>
         </is>
       </c>
     </row>
     <row r="555">
       <c r="A555" t="inlineStr">
         <is>
-          <t>Otofarma S.p.A.</t>
+          <t>Piu' Medical S.p.A.</t>
         </is>
       </c>
       <c r="B555" t="inlineStr">
@@ -18370,7 +18370,7 @@
     <row r="557">
       <c r="A557" t="inlineStr">
         <is>
-          <t>Piu' Medical S.p.A.</t>
+          <t>Otofarma S.p.A.</t>
         </is>
       </c>
       <c r="B557" t="inlineStr">
@@ -18387,7 +18387,7 @@
     <row r="558">
       <c r="A558" t="inlineStr">
         <is>
-          <t>Renovalo S.p.A.</t>
+          <t>OSAI Automation System S.p.A.</t>
         </is>
       </c>
       <c r="B558" t="inlineStr">
@@ -18397,14 +18397,14 @@
       </c>
       <c r="C558" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Bod Annual Report</t>
         </is>
       </c>
     </row>
     <row r="559">
       <c r="A559" t="inlineStr">
         <is>
-          <t>Seri Industrial S.p.A.</t>
+          <t>OPS Retail S.p.A.</t>
         </is>
       </c>
       <c r="B559" t="inlineStr">
@@ -18414,14 +18414,14 @@
       </c>
       <c r="C559" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Bod Annual Report</t>
         </is>
       </c>
     </row>
     <row r="560">
       <c r="A560" t="inlineStr">
         <is>
-          <t>Vantea Smart S.p.A.</t>
+          <t>Ambromobiliare S.p.A.</t>
         </is>
       </c>
       <c r="B560" t="inlineStr">
@@ -18438,7 +18438,7 @@
     <row r="561">
       <c r="A561" t="inlineStr">
         <is>
-          <t>Ambromobiliare S.p.A.</t>
+          <t>Casta Diva Group S.p.A.</t>
         </is>
       </c>
       <c r="B561" t="inlineStr">
@@ -18448,7 +18448,7 @@
       </c>
       <c r="C561" t="inlineStr">
         <is>
-          <t>Annual General Meeting</t>
+          <t>Bod Annual Report</t>
         </is>
       </c>
     </row>
@@ -18463,146 +18463,9 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J3"/>
+  <dimension ref="A1:A1"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <sheetData>
-    <row r="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>stock_name</t>
-        </is>
-      </c>
-      <c r="B1" s="1" t="inlineStr">
-        <is>
-          <t>ticker</t>
-        </is>
-      </c>
-      <c r="C1" s="1" t="inlineStr">
-        <is>
-          <t>detachment_date</t>
-        </is>
-      </c>
-      <c r="D1" s="1" t="inlineStr">
-        <is>
-          <t>payment_date</t>
-        </is>
-      </c>
-      <c r="E1" s="1" t="inlineStr">
-        <is>
-          <t>last_close</t>
-        </is>
-      </c>
-      <c r="F1" s="1" t="inlineStr">
-        <is>
-          <t>dividend</t>
-        </is>
-      </c>
-      <c r="G1" s="1" t="inlineStr">
-        <is>
-          <t>currency</t>
-        </is>
-      </c>
-      <c r="H1" s="1" t="inlineStr">
-        <is>
-          <t>ratio</t>
-        </is>
-      </c>
-      <c r="I1" s="1" t="inlineStr">
-        <is>
-          <t>miss_days</t>
-        </is>
-      </c>
-      <c r="J1" s="1" t="inlineStr">
-        <is>
-          <t>is_opportunity</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>B.F. S.p.A.</t>
-        </is>
-      </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>IT0005187460</t>
-        </is>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>2026-08-03 00:00:00</t>
-        </is>
-      </c>
-      <c r="D2" t="inlineStr">
-        <is>
-          <t>2026-08-05</t>
-        </is>
-      </c>
-      <c r="E2" t="n">
-        <v>4.940000057220459</v>
-      </c>
-      <c r="F2" t="n">
-        <v>0.038</v>
-      </c>
-      <c r="G2" t="inlineStr">
-        <is>
-          <t>EURO</t>
-        </is>
-      </c>
-      <c r="H2" t="n">
-        <v>0.7692307603207009</v>
-      </c>
-      <c r="I2" t="n">
-        <v>97</v>
-      </c>
-      <c r="J2" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>B.F. S.p.A.</t>
-        </is>
-      </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>IT0005187460</t>
-        </is>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>2026-09-28 00:00:00</t>
-        </is>
-      </c>
-      <c r="D3" t="inlineStr">
-        <is>
-          <t>2026-09-30</t>
-        </is>
-      </c>
-      <c r="E3" t="n">
-        <v>4.940000057220459</v>
-      </c>
-      <c r="F3" t="n">
-        <v>0.038</v>
-      </c>
-      <c r="G3" t="inlineStr">
-        <is>
-          <t>EURO</t>
-        </is>
-      </c>
-      <c r="H3" t="n">
-        <v>0.7692307603207009</v>
-      </c>
-      <c r="I3" t="n">
-        <v>153</v>
-      </c>
-      <c r="J3" t="b">
-        <v>0</v>
-      </c>
-    </row>
-  </sheetData>
+  <sheetData/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -18613,367 +18476,9 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C21"/>
+  <dimension ref="A1:A1"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <sheetData>
-    <row r="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>Stock</t>
-        </is>
-      </c>
-      <c r="B1" s="1" t="inlineStr">
-        <is>
-          <t>Date</t>
-        </is>
-      </c>
-      <c r="C1" s="1" t="inlineStr">
-        <is>
-          <t>Event</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>Ambromobiliare S.p.A.</t>
-        </is>
-      </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>2026-05-28</t>
-        </is>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Annual General Meeting</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>CROWDFUNDME S.p.A.</t>
-        </is>
-      </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>2026-05-28</t>
-        </is>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Annual General Meeting</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>Casta Diva Group S.p.A.</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>2026-05-28</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Bod Annual Report</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>Cube Labs S.p.A.</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>2026-05-28</t>
-        </is>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Bod Annual Report</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>Dexelance S.p.A.</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>2026-05-04</t>
-        </is>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Additional Periodic Financial Information</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>FAE Technology Società Benefit S.p.A.</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>2026-05-28</t>
-        </is>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Annual General Meeting</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>Generalfinance S.p.A.</t>
-        </is>
-      </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>2026-05-08</t>
-        </is>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Analyst Presentation</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>Intesa Sanpaolo S.p.A.</t>
-        </is>
-      </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>2026-05-08</t>
-        </is>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Additional Periodic Financial Information</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>Intesa Sanpaolo S.p.A.</t>
-        </is>
-      </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>2026-05-08</t>
-        </is>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Analyst Presentation</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>OPS Retail S.p.A.</t>
-        </is>
-      </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>2026-05-28</t>
-        </is>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>Bod Annual Report</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>OSAI Automation System S.p.A.</t>
-        </is>
-      </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>2026-05-28</t>
-        </is>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>Bod Annual Report</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>Otofarma S.p.A.</t>
-        </is>
-      </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>2026-05-28</t>
-        </is>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>Bod Annual Report</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>POLIGRAFICI PRINTING S.p.A.</t>
-        </is>
-      </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>2026-05-28</t>
-        </is>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>Annual General Meeting</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t>Piu' Medical S.p.A.</t>
-        </is>
-      </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>2026-05-28</t>
-        </is>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>Bod Annual Report</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t>Renovalo S.p.A.</t>
-        </is>
-      </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>2026-05-28</t>
-        </is>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>Annual General Meeting</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t>Sanlorenzo S.p.A.</t>
-        </is>
-      </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>2026-05-14</t>
-        </is>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>Analyst Presentation</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>Sanlorenzo S.p.A.</t>
-        </is>
-      </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>2026-05-21</t>
-        </is>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>Analyst Presentation</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t>Sanlorenzo S.p.A.</t>
-        </is>
-      </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>2026-05-22</t>
-        </is>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>Analyst Presentation</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" t="inlineStr">
-        <is>
-          <t>Seri Industrial S.p.A.</t>
-        </is>
-      </c>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>2026-05-28</t>
-        </is>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>Annual General Meeting</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" t="inlineStr">
-        <is>
-          <t>Vantea Smart S.p.A.</t>
-        </is>
-      </c>
-      <c r="B21" t="inlineStr">
-        <is>
-          <t>2026-05-28</t>
-        </is>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>Annual General Meeting</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
+  <sheetData/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>